--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,6 +117,12 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -194,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -254,6 +260,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -737,7 +746,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -807,7 +816,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -877,7 +886,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -947,7 +956,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -1017,7 +1026,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -1087,7 +1096,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -1157,7 +1166,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -1227,7 +1236,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -1235,7 +1244,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1245,12 +1254,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1260,12 +1269,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1275,7 +1284,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1306,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
@@ -1305,7 +1314,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1315,12 +1324,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1330,12 +1339,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1345,7 +1354,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1376,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -1375,7 +1384,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1385,12 +1394,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1400,12 +1409,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1415,7 +1424,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1446,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -1507,7 +1516,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -1577,7 +1586,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -1585,7 +1594,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1595,12 +1604,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1610,12 +1619,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1625,7 +1634,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1656,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -1655,7 +1664,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1665,12 +1674,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1680,12 +1689,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1695,7 +1704,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1726,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1725,7 +1734,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1735,12 +1744,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1750,12 +1759,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1765,7 +1774,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1796,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -1857,7 +1866,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -1927,7 +1936,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -1935,7 +1944,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1945,12 +1954,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1960,12 +1969,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1975,7 +1984,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2006,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
@@ -2005,7 +2014,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -2015,12 +2024,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2030,12 +2039,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2045,7 +2054,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2076,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -2075,7 +2084,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2085,12 +2094,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2100,12 +2109,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2115,7 +2124,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2146,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -2207,7 +2216,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -2277,7 +2286,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -2285,7 +2294,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2295,12 +2304,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2310,12 +2319,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2325,7 +2334,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2356,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -2355,7 +2364,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2365,12 +2374,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2380,12 +2389,12 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2395,7 +2404,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2426,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -2425,7 +2434,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2435,12 +2444,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2450,12 +2459,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2465,7 +2474,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2496,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
@@ -2557,7 +2566,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
@@ -2627,7 +2636,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -2635,7 +2644,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2645,12 +2654,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2660,12 +2669,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2675,7 +2684,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2706,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -2705,7 +2714,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2715,12 +2724,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2730,12 +2739,12 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2745,7 +2754,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2776,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -2775,7 +2784,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2785,12 +2794,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2800,12 +2809,12 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -2815,7 +2824,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2846,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -2907,7 +2916,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -2977,7 +2986,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -3047,7 +3056,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -3117,7 +3126,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
@@ -3187,7 +3196,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -3257,7 +3266,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -3327,7 +3336,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -3397,7 +3406,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
@@ -3467,7 +3476,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -3537,7 +3546,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
@@ -3607,7 +3616,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
@@ -3677,7 +3686,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
@@ -3747,7 +3756,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -3817,7 +3826,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
@@ -3887,7 +3896,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -3957,7 +3966,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -4027,7 +4036,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -4097,7 +4106,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
@@ -4167,7 +4176,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
@@ -4237,7 +4246,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -4307,7 +4316,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
@@ -4377,7 +4386,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
@@ -4447,7 +4456,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
@@ -4517,7 +4526,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
@@ -4587,7 +4596,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
@@ -4657,7 +4666,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
@@ -4727,7 +4736,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
@@ -4797,7 +4806,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
@@ -4867,7 +4876,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
@@ -4937,7 +4946,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
@@ -5007,7 +5016,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
@@ -5077,7 +5086,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
@@ -5147,7 +5156,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
@@ -5217,7 +5226,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -5287,7 +5296,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
@@ -5357,7 +5366,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
@@ -5427,7 +5436,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
@@ -5497,7 +5506,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
@@ -5567,7 +5576,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
@@ -5637,7 +5646,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
@@ -5707,7 +5716,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
@@ -5777,7 +5786,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
@@ -5847,7 +5856,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
@@ -5917,7 +5926,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
@@ -5987,7 +5996,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
@@ -6057,7 +6066,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
@@ -6127,7 +6136,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
@@ -6197,7 +6206,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
@@ -6267,7 +6276,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -6337,7 +6346,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
@@ -6407,7 +6416,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
@@ -6477,7 +6486,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
@@ -6547,7 +6556,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
@@ -6617,7 +6626,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
@@ -6687,7 +6696,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -6757,7 +6766,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
@@ -6827,7 +6836,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
@@ -6897,7 +6906,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
@@ -6967,7 +6976,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
@@ -7037,7 +7046,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
@@ -7107,7 +7116,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
@@ -7177,7 +7186,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
@@ -7247,7 +7256,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
@@ -7317,7 +7326,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
@@ -7387,7 +7396,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -7457,7 +7466,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
@@ -7527,7 +7536,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
@@ -7597,7 +7606,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E101" s="4" t="n">
@@ -7667,7 +7676,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
@@ -7737,7 +7746,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E103" s="4" t="n">
@@ -7807,7 +7816,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
@@ -7877,7 +7886,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E105" s="4" t="n">
@@ -7947,7 +7956,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
@@ -8017,7 +8026,7 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E107" s="4" t="n">
@@ -8087,7 +8096,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
@@ -8157,7 +8166,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E109" s="4" t="n">
@@ -8227,7 +8236,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
@@ -8297,7 +8306,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
@@ -8367,7 +8376,7 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
@@ -8437,7 +8446,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
@@ -8507,7 +8516,7 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
@@ -8577,7 +8586,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E115" s="4" t="n">
@@ -8647,7 +8656,7 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
@@ -8717,7 +8726,7 @@
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
@@ -8787,7 +8796,7 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
@@ -8857,7 +8866,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
@@ -8927,7 +8936,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
@@ -8997,7 +9006,7 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
@@ -9067,7 +9076,7 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
@@ -9137,7 +9146,7 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
@@ -9207,7 +9216,7 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
@@ -9277,7 +9286,7 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
@@ -9347,7 +9356,7 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
@@ -9417,7 +9426,7 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
@@ -9487,7 +9496,7 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
@@ -9557,7 +9566,7 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
@@ -9627,7 +9636,7 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
@@ -9697,7 +9706,7 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
@@ -9767,7 +9776,7 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -9837,7 +9846,7 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
@@ -9907,7 +9916,7 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -9977,7 +9986,7 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
@@ -10047,7 +10056,7 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
@@ -10117,7 +10126,7 @@
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
@@ -10187,7 +10196,7 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
@@ -10257,7 +10266,7 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
@@ -10327,7 +10336,7 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
@@ -10397,7 +10406,7 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
@@ -10467,7 +10476,7 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
@@ -10537,7 +10546,7 @@
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
@@ -10607,7 +10616,7 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
@@ -10677,7 +10686,7 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
@@ -10747,7 +10756,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
@@ -10817,7 +10826,7 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
@@ -10887,7 +10896,7 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
@@ -10957,7 +10966,7 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
@@ -11027,7 +11036,7 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
@@ -11097,7 +11106,7 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
@@ -11167,7 +11176,7 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
@@ -11237,7 +11246,7 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
@@ -11307,7 +11316,7 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
@@ -11377,7 +11386,7 @@
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
@@ -11447,7 +11456,7 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
@@ -11517,7 +11526,7 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
@@ -11587,7 +11596,7 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
@@ -11657,7 +11666,7 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
@@ -11727,7 +11736,7 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
@@ -11797,7 +11806,7 @@
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
@@ -11867,7 +11876,7 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
@@ -11937,7 +11946,7 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
@@ -12007,7 +12016,7 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
@@ -12077,7 +12086,7 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
@@ -12147,7 +12156,7 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
@@ -12217,7 +12226,7 @@
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
@@ -12287,7 +12296,7 @@
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
@@ -12357,7 +12366,7 @@
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
@@ -12427,7 +12436,7 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
@@ -12497,7 +12506,7 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
@@ -12567,7 +12576,7 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
@@ -12637,7 +12646,7 @@
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
@@ -12707,7 +12716,7 @@
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
@@ -12777,7 +12786,7 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
@@ -12847,7 +12856,7 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
@@ -12917,7 +12926,7 @@
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E177" s="4" t="n">
@@ -12987,7 +12996,7 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E178" s="4" t="n">
@@ -13057,7 +13066,7 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E179" s="4" t="n">
@@ -13127,7 +13136,7 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
@@ -13197,7 +13206,7 @@
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E181" s="4" t="n">
@@ -13267,7 +13276,7 @@
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E182" s="4" t="n">
@@ -13337,7 +13346,7 @@
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E183" s="4" t="n">
@@ -13407,7 +13416,7 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
@@ -13477,7 +13486,7 @@
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E185" s="4" t="n">
@@ -13547,7 +13556,7 @@
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E186" s="4" t="n">
@@ -13617,7 +13626,7 @@
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E187" s="4" t="n">
@@ -13687,7 +13696,7 @@
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E188" s="4" t="n">
@@ -13757,7 +13766,7 @@
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E189" s="4" t="n">
@@ -13827,7 +13836,7 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E190" s="4" t="n">
@@ -13897,7 +13906,7 @@
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E191" s="4" t="n">
@@ -13967,7 +13976,7 @@
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
@@ -14037,7 +14046,7 @@
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E193" s="4" t="n">
@@ -14107,7 +14116,7 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E194" s="4" t="n">
@@ -14177,7 +14186,7 @@
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E195" s="4" t="n">
@@ -14247,7 +14256,7 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
@@ -14376,27 +14385,27 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>179</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14469,7 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>A | 980呎 (暂无)
+          <t>A | 980呎 (3房)
 -
 -
 (待售)</t>
@@ -14468,7 +14477,7 @@
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>B | 1120呎 (暂无)
+          <t>B | 1120呎 (3房)
 -
 -
 (待售)</t>
@@ -14476,7 +14485,7 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>C | 861呎 (暂无)
+          <t>C | 861呎 (3房)
 -
 -
 (待售)</t>
@@ -14497,7 +14506,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>A | 1465呎 (暂无)
+          <t>A | 1465呎 (2房)
 -
 -
 (待售)</t>
@@ -14505,7 +14514,7 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>B | 1393呎 (暂无)
+          <t>B | 1393呎 (2房)
 -
 -
 (待售)</t>
@@ -14525,33 +14534,33 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 610呎 (暂无)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 767呎 (暂无)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 796呎 (暂无)
--
--
-(待售)</t>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 610呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 767呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 796呎 (3房)
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>D | 389呎 (暂无)
+          <t>D | 389呎 (2房)
 -
 -
 (待售)</t>
@@ -14559,7 +14568,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>E | 432呎 (暂无)
+          <t>E | 432呎 (2房)
 -
 -
 (待售)</t>
@@ -14576,33 +14585,33 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 610呎 (暂无)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 767呎 (暂无)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 799呎 (暂无)
--
--
-(待售)</t>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 610呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 767呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 799呎 (3房)
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>D | 389呎 (暂无)
+          <t>D | 389呎 (2房)
 -
 -
 (待售)</t>
@@ -14610,7 +14619,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>E | 432呎 (暂无)
+          <t>E | 432呎 (2房)
 -
 -
 (待售)</t>
@@ -14627,33 +14636,33 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 610呎 (暂无)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 767呎 (暂无)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 799呎 (暂无)
--
--
-(待售)</t>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 610呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 767呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 799呎 (3房)
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>D | 389呎 (暂无)
+          <t>D | 389呎 (2房)
 -
 -
 (待售)</t>
@@ -14661,7 +14670,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>E | 432呎 (暂无)
+          <t>E | 432呎 (2房)
 -
 -
 (待售)</t>
@@ -14678,33 +14687,33 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 610呎 (暂无)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 767呎 (暂无)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 799呎 (暂无)
--
--
-(待售)</t>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 610呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 767呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 799呎 (3房)
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>D | 389呎 (暂无)
+          <t>D | 389呎 (2房)
 -
 -
 (待售)</t>
@@ -14712,7 +14721,7 @@
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>E | 432呎 (暂无)
+          <t>E | 432呎 (2房)
 -
 -
 (待售)</t>
@@ -14729,33 +14738,33 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 610呎 (暂无)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 729呎 (暂无)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 792呎 (暂无)
--
--
-(待售)</t>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 610呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 729呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 792呎 (3房)
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
         <is>
-          <t>D | 389呎 (暂无)
+          <t>D | 389呎 (2房)
 -
 -
 (待售)</t>
@@ -14763,7 +14772,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>E | 432呎 (暂无)
+          <t>E | 432呎 (2房)
 -
 -
 (待售)</t>
@@ -14782,7 +14791,7 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>A | 602呎 (暂无)
+          <t>A | 602呎 (3房)
 -
 -
 (待售)</t>
@@ -14790,7 +14799,7 @@
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>B | 456呎 (暂无)
+          <t>B | 456呎 (2房)
 -
 -
 (待售)</t>
@@ -14798,7 +14807,7 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -14806,7 +14815,7 @@
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>D | 450呎 (暂无)
+          <t>D | 450呎 (2房)
 -
 -
 (待售)</t>
@@ -14814,7 +14823,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>E | 433呎 (暂无)
+          <t>E | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -14822,7 +14831,7 @@
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>F | 433呎 (暂无)
+          <t>F | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -14830,7 +14839,7 @@
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>G | 408呎 (暂无)
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
@@ -14847,7 +14856,7 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>A | 602呎 (暂无)
+          <t>A | 602呎 (3房)
 -
 -
 (待售)</t>
@@ -14855,7 +14864,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>B | 456呎 (暂无)
+          <t>B | 456呎 (2房)
 -
 -
 (待售)</t>
@@ -14863,7 +14872,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -14871,7 +14880,7 @@
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -14879,7 +14888,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>E | 433呎 (暂无)
+          <t>E | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -14887,7 +14896,7 @@
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>F | 433呎 (暂无)
+          <t>F | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -14895,7 +14904,7 @@
       </c>
       <c r="H13" s="19" t="inlineStr">
         <is>
-          <t>G | 408呎 (暂无)
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
@@ -14912,7 +14921,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>A | 602呎 (暂无)
+          <t>A | 602呎 (3房)
 -
 -
 (待售)</t>
@@ -14920,7 +14929,7 @@
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
-          <t>B | 456呎 (暂无)
+          <t>B | 456呎 (2房)
 -
 -
 (待售)</t>
@@ -14928,7 +14937,7 @@
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -14936,7 +14945,7 @@
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -14944,7 +14953,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>E | 433呎 (暂无)
+          <t>E | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -14952,7 +14961,7 @@
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
-          <t>F | 433呎 (暂无)
+          <t>F | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -14960,7 +14969,7 @@
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>G | 408呎 (暂无)
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
@@ -14977,7 +14986,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>A | 602呎 (暂无)
+          <t>A | 602呎 (3房)
 -
 -
 (待售)</t>
@@ -14985,7 +14994,7 @@
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>B | 456呎 (暂无)
+          <t>B | 456呎 (2房)
 -
 -
 (待售)</t>
@@ -14993,7 +15002,7 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15001,7 +15010,7 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15009,7 +15018,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>E | 433呎 (暂无)
+          <t>E | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -15017,7 +15026,7 @@
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>F | 433呎 (暂无)
+          <t>F | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -15025,7 +15034,7 @@
       </c>
       <c r="H15" s="19" t="inlineStr">
         <is>
-          <t>G | 408呎 (暂无)
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
@@ -15042,7 +15051,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>A | 602呎 (暂无)
+          <t>A | 602呎 (3房)
 -
 -
 (待售)</t>
@@ -15050,7 +15059,7 @@
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
-          <t>B | 456呎 (暂无)
+          <t>B | 456呎 (2房)
 -
 -
 (待售)</t>
@@ -15058,7 +15067,7 @@
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15066,7 +15075,7 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15074,7 +15083,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>E | 433呎 (暂无)
+          <t>E | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -15082,7 +15091,7 @@
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>F | 433呎 (暂无)
+          <t>F | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -15090,7 +15099,7 @@
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>G | 408呎 (暂无)
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
@@ -15107,7 +15116,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>A | 602呎 (暂无)
+          <t>A | 602呎 (3房)
 -
 -
 (待售)</t>
@@ -15115,7 +15124,7 @@
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
-          <t>B | 456呎 (暂无)
+          <t>B | 456呎 (2房)
 -
 -
 (待售)</t>
@@ -15123,7 +15132,7 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15131,7 +15140,7 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15139,7 +15148,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>E | 433呎 (暂无)
+          <t>E | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -15147,7 +15156,7 @@
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>F | 433呎 (暂无)
+          <t>F | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -15155,7 +15164,7 @@
       </c>
       <c r="H17" s="19" t="inlineStr">
         <is>
-          <t>G | 408呎 (暂无)
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
@@ -15172,7 +15181,7 @@
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>A | 602呎 (暂无)
+          <t>A | 602呎 (3房)
 -
 -
 (待售)</t>
@@ -15180,7 +15189,7 @@
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>B | 456呎 (暂无)
+          <t>B | 456呎 (2房)
 -
 -
 (待售)</t>
@@ -15188,7 +15197,7 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15196,7 +15205,7 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15204,7 +15213,7 @@
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>E | 433呎 (暂无)
+          <t>E | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -15212,7 +15221,7 @@
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>F | 433呎 (暂无)
+          <t>F | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -15220,7 +15229,7 @@
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>G | 408呎 (暂无)
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
@@ -15237,7 +15246,7 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>A | 602呎 (暂无)
+          <t>A | 602呎 (3房)
 -
 -
 (待售)</t>
@@ -15245,7 +15254,7 @@
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>B | 456呎 (暂无)
+          <t>B | 456呎 (2房)
 -
 -
 (待售)</t>
@@ -15253,7 +15262,7 @@
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15261,7 +15270,7 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15269,7 +15278,7 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>E | 433呎 (暂无)
+          <t>E | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -15277,7 +15286,7 @@
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>F | 433呎 (暂无)
+          <t>F | 433呎 (2房)
 -
 -
 (待售)</t>
@@ -15285,7 +15294,7 @@
       </c>
       <c r="H19" s="19" t="inlineStr">
         <is>
-          <t>G | 408呎 (暂无)
+          <t>G | 408呎 (2房)
 -
 -
 (待售)</t>
@@ -15302,7 +15311,7 @@
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -15310,7 +15319,7 @@
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -15318,7 +15327,7 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15326,7 +15335,7 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15334,7 +15343,7 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15342,7 +15351,7 @@
       </c>
       <c r="G20" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15350,7 +15359,7 @@
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -15358,7 +15367,7 @@
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15366,7 +15375,7 @@
       </c>
       <c r="J20" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -15381,7 +15390,7 @@
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -15389,7 +15398,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -15397,7 +15406,7 @@
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15405,7 +15414,7 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15413,7 +15422,7 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15421,7 +15430,7 @@
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15429,7 +15438,7 @@
       </c>
       <c r="H21" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -15437,7 +15446,7 @@
       </c>
       <c r="I21" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15445,7 +15454,7 @@
       </c>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -15460,7 +15469,7 @@
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -15468,7 +15477,7 @@
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -15476,7 +15485,7 @@
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15484,7 +15493,7 @@
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15492,7 +15501,7 @@
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15500,7 +15509,7 @@
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15508,7 +15517,7 @@
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -15516,7 +15525,7 @@
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15524,7 +15533,7 @@
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -15539,7 +15548,7 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -15547,7 +15556,7 @@
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -15555,7 +15564,7 @@
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15563,7 +15572,7 @@
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15571,7 +15580,7 @@
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15579,7 +15588,7 @@
       </c>
       <c r="G23" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15587,7 +15596,7 @@
       </c>
       <c r="H23" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -15595,7 +15604,7 @@
       </c>
       <c r="I23" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15603,7 +15612,7 @@
       </c>
       <c r="J23" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -15618,7 +15627,7 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -15626,7 +15635,7 @@
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -15634,7 +15643,7 @@
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15642,7 +15651,7 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15650,7 +15659,7 @@
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15658,7 +15667,7 @@
       </c>
       <c r="G24" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15666,7 +15675,7 @@
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -15674,7 +15683,7 @@
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15682,7 +15691,7 @@
       </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -15697,7 +15706,7 @@
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -15705,7 +15714,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -15713,7 +15722,7 @@
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15721,7 +15730,7 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15729,7 +15738,7 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15737,7 +15746,7 @@
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15745,7 +15754,7 @@
       </c>
       <c r="H25" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -15753,7 +15762,7 @@
       </c>
       <c r="I25" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15761,7 +15770,7 @@
       </c>
       <c r="J25" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -15776,7 +15785,7 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -15784,7 +15793,7 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -15792,7 +15801,7 @@
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15800,7 +15809,7 @@
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15808,7 +15817,7 @@
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15816,7 +15825,7 @@
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15824,7 +15833,7 @@
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -15832,7 +15841,7 @@
       </c>
       <c r="I26" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15840,7 +15849,7 @@
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -15855,7 +15864,7 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -15863,7 +15872,7 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -15871,7 +15880,7 @@
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15879,7 +15888,7 @@
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15887,7 +15896,7 @@
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15895,7 +15904,7 @@
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15903,7 +15912,7 @@
       </c>
       <c r="H27" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -15911,7 +15920,7 @@
       </c>
       <c r="I27" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15919,7 +15928,7 @@
       </c>
       <c r="J27" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -15934,7 +15943,7 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -15942,7 +15951,7 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -15950,7 +15959,7 @@
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -15958,7 +15967,7 @@
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -15966,7 +15975,7 @@
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15974,7 +15983,7 @@
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15982,7 +15991,7 @@
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -15990,7 +15999,7 @@
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -15998,7 +16007,7 @@
       </c>
       <c r="J28" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -16013,7 +16022,7 @@
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -16021,7 +16030,7 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -16029,7 +16038,7 @@
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -16037,7 +16046,7 @@
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -16045,7 +16054,7 @@
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -16053,7 +16062,7 @@
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -16061,7 +16070,7 @@
       </c>
       <c r="H29" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -16069,7 +16078,7 @@
       </c>
       <c r="I29" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -16077,7 +16086,7 @@
       </c>
       <c r="J29" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -16092,7 +16101,7 @@
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -16100,7 +16109,7 @@
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -16108,7 +16117,7 @@
       </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>C | 316呎 (暂无)
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
@@ -16116,7 +16125,7 @@
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>D | 451呎 (暂无)
+          <t>D | 451呎 (2房)
 -
 -
 (待售)</t>
@@ -16124,7 +16133,7 @@
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>E | 304呎 (暂无)
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -16132,7 +16141,7 @@
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -16140,7 +16149,7 @@
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -16148,7 +16157,7 @@
       </c>
       <c r="I30" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -16156,7 +16165,7 @@
       </c>
       <c r="J30" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
@@ -16171,7 +16180,7 @@
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>A | 428呎 (暂无)
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
@@ -16179,7 +16188,7 @@
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>B | 453呎 (暂无)
+          <t>B | 453呎 (2房)
 -
 -
 (待售)</t>
@@ -16187,7 +16196,7 @@
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>C | 277呎 (暂无)
+          <t>C | 277呎 (1房)
 -
 -
 (待售)</t>
@@ -16195,7 +16204,7 @@
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>D | 413呎 (暂无)
+          <t>D | 413呎 (2房)
 -
 -
 (待售)</t>
@@ -16203,7 +16212,7 @@
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>E | 305呎 (暂无)
+          <t>E | 305呎 (1房)
 -
 -
 (待售)</t>
@@ -16211,7 +16220,7 @@
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
-          <t>F | 304呎 (暂无)
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -16219,7 +16228,7 @@
       </c>
       <c r="H31" s="19" t="inlineStr">
         <is>
-          <t>G | 301呎 (暂无)
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
@@ -16227,7 +16236,7 @@
       </c>
       <c r="I31" s="19" t="inlineStr">
         <is>
-          <t>H | 304呎 (暂无)
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
@@ -16235,7 +16244,7 @@
       </c>
       <c r="J31" s="19" t="inlineStr">
         <is>
-          <t>J | 302呎 (暂无)
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>

--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -17,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="19">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -114,13 +116,18 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -200,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -212,6 +219,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -256,13 +266,16 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -640,12 +653,12 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -754,7 +767,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -764,12 +777,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -779,12 +792,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -794,7 +807,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -824,7 +837,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -834,12 +847,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -849,12 +862,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -864,7 +877,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -894,7 +907,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -904,12 +917,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -919,12 +932,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -934,7 +947,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -964,7 +977,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -974,12 +987,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -989,12 +1002,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1004,7 +1017,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1047,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1044,12 +1057,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1059,12 +1072,12 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1074,7 +1087,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4547,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4542,34 +4555,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H57" s="5" t="n">
+        <v>12845000</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>28481</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>10147550</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>22500</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -5024,7 +5029,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -5032,34 +5037,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H64" s="5" t="n">
+        <v>12717000</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>28197</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>10046430</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>22276</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -5514,7 +5511,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -5522,34 +5519,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H71" s="5" t="n">
+        <v>12590000</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>27916</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>9946100</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>22053</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
@@ -6004,7 +5993,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -6012,34 +6001,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H78" s="5" t="n">
+        <v>12466000</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>27641</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>9848140</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>21836</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -6214,7 +6195,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6222,34 +6203,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H81" s="5" t="n">
+        <v>18252000</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>30319</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>14419080</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>23952</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
@@ -6494,7 +6467,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6502,34 +6475,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H85" s="5" t="n">
+        <v>12344000</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>27370</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L85" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>9751760</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>21623</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
@@ -6704,7 +6669,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6712,34 +6677,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H88" s="5" t="n">
+        <v>18073000</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>30022</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>14277670</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>23717</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -7124,7 +7081,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -7132,34 +7089,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H94" s="5" t="n">
+        <v>12221000</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>27098</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>9654590</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>21407</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
@@ -7264,7 +7213,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -7272,34 +7221,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H96" s="5" t="n">
+        <v>11684000</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>25792</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L96" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>9230360</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>20376</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -7754,7 +7695,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -7762,34 +7703,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H103" s="5" t="n">
+        <v>12149000</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>26938</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>9597710</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>21281</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr">
@@ -7894,7 +7827,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7902,34 +7835,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H105" s="5" t="n">
+        <v>11616000</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>25642</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>9176640</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>20257</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr">
@@ -8384,7 +8309,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -8392,34 +8317,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H112" s="5" t="n">
+        <v>12075000</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>26774</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L112" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>9539250</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>21151</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
@@ -8524,7 +8441,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -8532,34 +8449,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I114" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H114" s="5" t="n">
+        <v>11546000</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>25488</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K114" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L114" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>9121340</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>20135</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -9014,7 +8923,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -9022,34 +8931,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H121" s="5" t="n">
+        <v>12003000</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>26614</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L121" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>9482370</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>21025</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N121" s="3" t="inlineStr">
@@ -9154,7 +9055,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -9162,34 +9063,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H123" s="5" t="n">
+        <v>11476000</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>25333</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L123" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>9066040</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>20013</v>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N123" s="3" t="inlineStr">
@@ -9644,7 +9537,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -9652,34 +9545,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H130" s="5" t="n">
+        <v>11932000</v>
+      </c>
+      <c r="I130" s="5" t="n">
+        <v>26457</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L130" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>9426280</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>20901</v>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N130" s="3" t="inlineStr">
@@ -9784,7 +9669,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -9792,34 +9677,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I132" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H132" s="5" t="n">
+        <v>11409000</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>25185</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K132" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L132" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>9013110</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>19896</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
@@ -10134,7 +10011,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -10142,34 +10019,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H137" s="5" t="n">
+        <v>8159000</v>
+      </c>
+      <c r="I137" s="5" t="n">
+        <v>26839</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>6445610</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>21203</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
@@ -10204,7 +10073,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -10212,34 +10081,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H138" s="5" t="n">
+        <v>8159000</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>26839</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L138" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>6445610</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>21203</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N138" s="3" t="inlineStr">
@@ -10274,7 +10135,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -10282,34 +10143,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H139" s="5" t="n">
+        <v>11861000</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>26299</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K139" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L139" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>9370190</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>20776</v>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N139" s="3" t="inlineStr">
@@ -10344,7 +10197,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -10352,34 +10205,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H140" s="5" t="n">
+        <v>7768000</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>24582</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L140" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>6136720</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>19420</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N140" s="3" t="inlineStr">
@@ -10414,7 +10259,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -10422,34 +10267,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H141" s="5" t="n">
+        <v>11341000</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>25035</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L141" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>8959390</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>19778</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -10764,7 +10601,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10772,34 +10609,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H146" s="5" t="n">
+        <v>8094000</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>26625</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L146" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>6394260</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>21034</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N146" s="3" t="inlineStr">
@@ -10834,7 +10663,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -10842,34 +10671,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H147" s="5" t="n">
+        <v>8094000</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>26625</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L147" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>6394260</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>21034</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N147" s="3" t="inlineStr">
@@ -10904,7 +10725,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -10912,34 +10733,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H148" s="5" t="n">
+        <v>11766000</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>26089</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L148" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>9295140</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>20610</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N148" s="3" t="inlineStr">
@@ -10974,7 +10787,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -10982,34 +10795,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H149" s="5" t="n">
+        <v>7722000</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>24437</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L149" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>6100380</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>19305</v>
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N149" s="3" t="inlineStr">
@@ -11044,7 +10849,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -11052,34 +10857,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H150" s="5" t="n">
+        <v>11273000</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>24885</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L150" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>8905670</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>19659</v>
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N150" s="3" t="inlineStr">
@@ -11394,7 +11191,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -11402,34 +11199,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I155" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H155" s="5" t="n">
+        <v>8030000</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>26414</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K155" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L155" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>6343700</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>20867</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N155" s="3" t="inlineStr">
@@ -11464,7 +11253,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -11472,34 +11261,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I156" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H156" s="5" t="n">
+        <v>8030000</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>26414</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K156" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L156" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>6343700</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>20867</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N156" s="3" t="inlineStr">
@@ -11534,7 +11315,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -11542,34 +11323,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H157" s="5" t="n">
+        <v>11673000</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>25882</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L157" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>9221670</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>20447</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
@@ -11604,7 +11377,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -11612,34 +11385,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I158" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H158" s="5" t="n">
+        <v>7676000</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>24291</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K158" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L158" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>6064040</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>19190</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N158" s="3" t="inlineStr">
@@ -11674,7 +11439,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -11682,34 +11447,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H159" s="5" t="n">
+        <v>11207000</v>
+      </c>
+      <c r="I159" s="5" t="n">
+        <v>24740</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L159" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>8853530</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>19544</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N159" s="3" t="inlineStr">
@@ -12024,7 +11781,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -12032,34 +11789,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H164" s="5" t="n">
+        <v>7965000</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>26201</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L164" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>6292350</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>20699</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N164" s="3" t="inlineStr">
@@ -12094,7 +11843,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -12102,34 +11851,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H165" s="5" t="n">
+        <v>7965000</v>
+      </c>
+      <c r="I165" s="5" t="n">
+        <v>26201</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L165" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>6292350</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>20699</v>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N165" s="3" t="inlineStr">
@@ -12164,7 +11905,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -12172,34 +11913,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I166" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H166" s="5" t="n">
+        <v>11580000</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>25676</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K166" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L166" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>9148200</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>20284</v>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N166" s="3" t="inlineStr">
@@ -12234,7 +11967,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -12242,34 +11975,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H167" s="5" t="n">
+        <v>7631000</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>24149</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L167" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>6028490</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>19078</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N167" s="3" t="inlineStr">
@@ -12304,7 +12029,7 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -12312,34 +12037,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H168" s="5" t="n">
+        <v>11140000</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>24592</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L168" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>8800600</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>19427</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
@@ -12654,7 +12371,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -12662,34 +12379,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H173" s="5" t="n">
+        <v>7888000</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>25947</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L173" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>6231520</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>20498</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -12724,7 +12433,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -12732,34 +12441,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H174" s="5" t="n">
+        <v>7888000</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>25947</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L174" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>6231520</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>20498</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N174" s="3" t="inlineStr">
@@ -12794,7 +12495,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -12802,34 +12503,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H175" s="5" t="n">
+        <v>11466000</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>25424</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L175" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>9058140</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>20085</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N175" s="3" t="inlineStr">
@@ -12864,7 +12557,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -12872,34 +12565,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H176" s="5" t="n">
+        <v>7585000</v>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>24003</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L176" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>5992150</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>18962</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N176" s="3" t="inlineStr">
@@ -12934,7 +12619,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -12942,34 +12627,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H177" s="5" t="n">
+        <v>11073000</v>
+      </c>
+      <c r="I177" s="5" t="n">
+        <v>24444</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L177" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>8747670</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>19311</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -13284,7 +12961,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -13292,34 +12969,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H182" s="5" t="n">
+        <v>7809000</v>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>25688</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L182" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>6169110</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>20293</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -13354,7 +13023,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -13362,34 +13031,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H183" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I183" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H183" s="5" t="n">
+        <v>7809000</v>
+      </c>
+      <c r="I183" s="5" t="n">
+        <v>25688</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K183" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L183" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>6169110</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>20293</v>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N183" s="3" t="inlineStr">
@@ -13424,7 +13085,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -13432,34 +13093,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H184" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I184" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H184" s="5" t="n">
+        <v>11352000</v>
+      </c>
+      <c r="I184" s="5" t="n">
+        <v>25171</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K184" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L184" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>8968080</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>19885</v>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N184" s="3" t="inlineStr">
@@ -13494,7 +13147,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -13502,34 +13155,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H185" s="5" t="n">
+        <v>7540000</v>
+      </c>
+      <c r="I185" s="5" t="n">
+        <v>23861</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L185" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>5956600</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>18850</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N185" s="3" t="inlineStr">
@@ -13564,7 +13209,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -13572,34 +13217,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H186" s="5" t="n">
+        <v>10963000</v>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>24201</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L186" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>8660770</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>19119</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N186" s="3" t="inlineStr">
@@ -13914,7 +13551,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -13922,34 +13559,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H191" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I191" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H191" s="5" t="n">
+        <v>7655000</v>
+      </c>
+      <c r="I191" s="5" t="n">
+        <v>25181</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K191" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L191" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>6047450</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>19893</v>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N191" s="3" t="inlineStr">
@@ -13984,7 +13613,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -13992,34 +13621,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H192" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I192" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H192" s="5" t="n">
+        <v>7682000</v>
+      </c>
+      <c r="I192" s="5" t="n">
+        <v>25187</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K192" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L192" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>6068780</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>19898</v>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N192" s="3" t="inlineStr">
@@ -14194,7 +13815,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -14202,34 +13823,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H195" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I195" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H195" s="5" t="n">
+        <v>10855000</v>
+      </c>
+      <c r="I195" s="5" t="n">
+        <v>23962</v>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K195" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L195" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>8575450</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>18930</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N195" s="3" t="inlineStr">
@@ -14339,202 +13952,202 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>皇璇 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>179</t>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>124</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I4" s="18" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 980呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 1120呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-      <c r="J5" s="20" t="inlineStr"/>
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 1465呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 1393呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
 招标单位
@@ -14542,7 +14155,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 767呎 (3房)
 招标单位
@@ -14550,7 +14163,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 796呎 (3房)
 招标单位
@@ -14558,7 +14171,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 -
@@ -14566,7 +14179,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 -
@@ -14574,18 +14187,18 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
 招标单位
@@ -14593,7 +14206,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 767呎 (3房)
 招标单位
@@ -14601,7 +14214,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
 招标单位
@@ -14609,7 +14222,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 -
@@ -14617,7 +14230,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 -
@@ -14625,18 +14238,18 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
-      <c r="I8" s="20" t="inlineStr"/>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+      <c r="H8" s="21" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
 招标单位
@@ -14644,7 +14257,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 767呎 (3房)
 招标单位
@@ -14652,7 +14265,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
 招标单位
@@ -14660,7 +14273,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 -
@@ -14668,7 +14281,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 -
@@ -14676,18 +14289,18 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
+      <c r="H9" s="21" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
 招标单位
@@ -14695,7 +14308,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 767呎 (3房)
 招标单位
@@ -14703,7 +14316,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
 招标单位
@@ -14711,7 +14324,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 -
@@ -14719,7 +14332,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 -
@@ -14727,18 +14340,18 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+      <c r="H10" s="21" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
 招标单位
@@ -14746,7 +14359,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 729呎 (3房)
 招标单位
@@ -14754,7 +14367,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 792呎 (3房)
 招标单位
@@ -14762,7 +14375,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 -
@@ -14770,7 +14383,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 -
@@ -14778,18 +14391,18 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="20" t="inlineStr"/>
-      <c r="I11" s="20" t="inlineStr"/>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
+      <c r="H11" s="21" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 -
@@ -14797,7 +14410,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 -
@@ -14805,7 +14418,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 -
@@ -14813,7 +14426,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 450呎 (2房)
 -
@@ -14821,7 +14434,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -14829,7 +14442,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 -
@@ -14837,7 +14450,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -14845,16 +14458,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 -
@@ -14862,7 +14475,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 -
@@ -14870,7 +14483,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 -
@@ -14878,7 +14491,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 -
@@ -14886,7 +14499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -14894,7 +14507,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 -
@@ -14902,7 +14515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H13" s="19" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -14910,16 +14523,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 -
@@ -14927,7 +14540,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 -
@@ -14935,7 +14548,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 -
@@ -14943,7 +14556,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 -
@@ -14951,7 +14564,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -14959,7 +14572,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 -
@@ -14967,7 +14580,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H14" s="19" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -14975,16 +14588,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
-      <c r="J14" s="20" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 -
@@ -14992,7 +14605,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 -
@@ -15000,7 +14613,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 -
@@ -15008,15 +14621,80 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
+$1284万
+$28,481/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 408呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 602呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 316呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 451呎 (2房)
+$1272万
+$28,197/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -15024,7 +14702,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 -
@@ -15032,7 +14710,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H15" s="19" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -15040,16 +14718,16 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 -
@@ -15057,7 +14735,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 -
@@ -15065,7 +14743,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 -
@@ -15073,15 +14751,80 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
+$1259万
+$27,916/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 408呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 602呎 (3房)
+$1825万
+$30,319/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 316呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 451呎 (2房)
+$1247万
+$27,641/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -15089,7 +14832,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 -
@@ -15097,7 +14840,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -15105,32 +14848,97 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
-      <c r="J16" s="20" t="inlineStr"/>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
+$1807万
+$30,022/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 456呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 451呎 (2房)
+$1234万
+$27,370/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 408呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 428呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 453呎 (2房)
+$1168万
+$25,792/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 -
@@ -15138,64 +14946,78 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
+$1222万
+$27,098/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>F | 433呎 (2房)
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr">
-        <is>
-          <t>G | 408呎 (2房)
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
-      <c r="J17" s="20" t="inlineStr"/>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 602呎 (3房)
+      <c r="J20" s="22" t="inlineStr">
+        <is>
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 453呎 (2房)
+$1162万
+$25,642/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 -
@@ -15203,64 +15025,78 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
+$1215万
+$26,938/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>F | 433呎 (2房)
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>G | 408呎 (2房)
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 602呎 (3房)
+      <c r="J21" s="22" t="inlineStr">
+        <is>
+          <t>J | 302呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 456呎 (2房)
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 428呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 453呎 (2房)
+$1155万
+$25,488/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 -
@@ -15268,48 +15104,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
+$1208万
+$26,774/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>E | 433呎 (2房)
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>F | 433呎 (2房)
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>G | 408呎 (2房)
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr"/>
-      <c r="J19" s="20" t="inlineStr"/>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>J | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 -
@@ -15317,15 +15167,94 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
+$1148万
+$25,333/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 316呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 451呎 (2房)
+$1200万
+$26,614/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 428呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 453呎 (2房)
+$1141万
+$25,185/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 -
@@ -15333,31 +15262,268 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
+$1193万
+$26,457/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 428呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 453呎 (2房)
+$1134万
+$25,035/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 316呎 (1房)
+$777万
+$24,582/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 451呎 (2房)
+$1186万
+$26,299/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
+$816万
+$26,839/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>F | 304呎 (1房)
+$816万
+$26,839/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 428呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 453呎 (2房)
+$1127万
+$24,885/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 316呎 (1房)
+$772万
+$24,437/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>D | 451呎 (2房)
+$1177万
+$26,089/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+$809万
+$26,625/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
+$809万
+$26,625/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="22" t="inlineStr">
+        <is>
+          <t>J | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 428呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 453呎 (2房)
+$1121万
+$24,740/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 316呎 (1房)
+$768万
+$24,291/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>D | 451呎 (2房)
+$1167万
+$25,882/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+$803万
+$26,414/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>F | 304呎 (1房)
+$803万
+$26,414/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 -
@@ -15365,7 +15531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 -
@@ -15373,7 +15539,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="J27" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15382,13 +15548,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 -
@@ -15396,853 +15562,300 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
+$1114万
+$24,592/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 316呎 (1房)
+$763万
+$24,149/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>D | 451呎 (2房)
+$1158万
+$25,676/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+$796万
+$26,201/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>F | 304呎 (1房)
+$796万
+$26,201/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>J | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 428呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>B | 453呎 (2房)
+$1107万
+$24,444/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
+$758万
+$24,003/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>D | 451呎 (2房)
+$1147万
+$25,424/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+$789万
+$25,947/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>F | 304呎 (1房)
+$789万
+$25,947/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>J | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 428呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 453呎 (2房)
+$1096万
+$24,201/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>C | 316呎 (1房)
+$754万
+$23,861/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
+$1135万
+$25,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>E | 304呎 (1房)
+$781万
+$25,688/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>F | 304呎 (1房)
+$781万
+$25,688/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>J | 302呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 428呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 453呎 (2房)
+$1086万
+$23,962/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 277呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 413呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+$768万
+$25,187/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
+$766万
+$25,181/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>G | 301呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>H | 304呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>J | 302呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>J | 302呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>D | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="inlineStr">
-        <is>
-          <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="19" t="inlineStr">
-        <is>
-          <t>J | 302呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>D | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="19" t="inlineStr">
-        <is>
-          <t>J | 302呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>D | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="19" t="inlineStr">
-        <is>
-          <t>J | 302呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>D | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="19" t="inlineStr">
-        <is>
-          <t>J | 302呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>D | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="19" t="inlineStr">
-        <is>
-          <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="19" t="inlineStr">
-        <is>
-          <t>J | 302呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>D | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="19" t="inlineStr">
-        <is>
-          <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="19" t="inlineStr">
-        <is>
-          <t>J | 302呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>B | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>D | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="19" t="inlineStr">
-        <is>
-          <t>J | 302呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>B | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>D | 451呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="19" t="inlineStr">
-        <is>
-          <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="19" t="inlineStr">
-        <is>
-          <t>J | 302呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>B | 453呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>C | 277呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>D | 413呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
+      <c r="J31" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -

--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,6 +122,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
@@ -207,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -272,10 +277,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -652,11 +660,11 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -977,38 +985,30 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>58506000</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>42000</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K6" s="5" t="n">
+        <v>58506000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>42000</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1047,38 +1047,30 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>58600000</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>40000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K7" s="5" t="n">
+        <v>58600000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>40000</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1087,7 +1079,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1257,38 +1249,30 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>31432000</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>39487</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K10" s="5" t="n">
+        <v>31432000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>39487</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1281,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1747,38 +1731,30 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>21960000</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>36000</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K17" s="5" t="n">
+        <v>21960000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>36000</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1787,7 +1763,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2027,38 +2003,30 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>24544000</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>32000</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K21" s="5" t="n">
+        <v>24544000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>32000</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2067,7 +2035,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2097,38 +2065,30 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>20130000</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>33000</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K22" s="5" t="n">
+        <v>20130000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>33000</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2137,7 +2097,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2307,38 +2267,30 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>25565500</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>31997</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K25" s="5" t="n">
+        <v>25565500</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>31997</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2347,7 +2299,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2377,38 +2329,30 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>23010000</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>30000</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K26" s="5" t="n">
+        <v>23010000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>30000</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2417,7 +2361,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2447,38 +2391,30 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>19215000</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>31500</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K27" s="5" t="n">
+        <v>19215000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>31500</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2487,7 +2423,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2657,38 +2593,30 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>24552000</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>31000</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K30" s="5" t="n">
+        <v>24552000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>31000</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -2697,7 +2625,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2727,38 +2655,30 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>21141000</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>29000</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K31" s="5" t="n">
+        <v>21141000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>29000</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2767,7 +2687,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2797,38 +2717,30 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>18300000</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>30000</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K32" s="5" t="n">
+        <v>18300000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>30000</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -2837,7 +2749,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2849,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2945,34 +2857,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H34" s="5" t="n">
+        <v>14375000</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>33199</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>11356250</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>26227</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3007,7 +2911,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3015,34 +2919,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H35" s="5" t="n">
+        <v>14375000</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>33199</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>11356250</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>26227</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -3147,7 +3043,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3155,34 +3051,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H37" s="5" t="n">
+        <v>8403000</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>26592</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>6638370</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>21008</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -3217,7 +3105,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3225,34 +3113,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H38" s="5" t="n">
+        <v>12288000</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>26947</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>9707520</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>21288</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -3427,7 +3307,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3435,34 +3315,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H41" s="5" t="n">
+        <v>14025000</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>32390</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>11079750</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>25588</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -3497,7 +3369,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3505,34 +3377,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H42" s="5" t="n">
+        <v>14657000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>33850</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>11579030</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>26741</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -3637,7 +3501,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3645,34 +3509,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H44" s="5" t="n">
+        <v>8378000</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>26513</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>6618620</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>20945</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -3707,7 +3563,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3715,34 +3571,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H45" s="5" t="n">
+        <v>12252000</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>26868</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>9679080</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>21226</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -3777,7 +3625,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3785,34 +3633,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H46" s="5" t="n">
+        <v>19374000</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>32183</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>15305460</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>25424</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -3917,7 +3757,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3925,34 +3765,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H48" s="5" t="n">
+        <v>13683000</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>31600</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>10809570</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>24964</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -3987,7 +3819,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3995,34 +3827,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H49" s="5" t="n">
+        <v>13683000</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>31600</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>10809570</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>24964</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -4127,7 +3951,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -4135,34 +3959,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H51" s="5" t="n">
+        <v>8352000</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>26430</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>6598080</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>20880</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -4197,7 +4013,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4205,34 +4021,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H52" s="5" t="n">
+        <v>12216000</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>26789</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>9650640</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>21164</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -4267,7 +4075,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4275,34 +4083,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H53" s="5" t="n">
+        <v>19088000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>31708</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>15079520</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>25049</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -4407,7 +4207,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4415,34 +4215,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H55" s="5" t="n">
+        <v>13350000</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>30831</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>10546500</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>24357</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -4477,7 +4269,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -4485,34 +4277,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H56" s="5" t="n">
+        <v>13350000</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>30831</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>10546500</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>24357</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -4609,7 +4393,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4617,34 +4401,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H58" s="5" t="n">
+        <v>8164000</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>25835</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>6449560</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>20410</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -4679,7 +4455,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4687,34 +4463,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H59" s="5" t="n">
+        <v>12179000</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>26708</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>9621410</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>21100</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -4749,7 +4517,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4757,34 +4525,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H60" s="5" t="n">
+        <v>18806000</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>31239</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>14856740</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>24679</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -4889,7 +4649,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4897,34 +4657,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H62" s="5" t="n">
+        <v>13088000</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>30226</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>10339520</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>23879</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -4959,7 +4711,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4967,34 +4719,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H63" s="5" t="n">
+        <v>13088000</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>30226</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>10339520</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>23879</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -5091,7 +4835,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -5099,34 +4843,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H65" s="5" t="n">
+        <v>8140000</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>25759</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>6430600</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>20350</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -5161,7 +4897,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -5169,34 +4905,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H66" s="5" t="n">
+        <v>12142000</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>26627</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>9592180</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>21035</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -5231,7 +4959,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -5239,34 +4967,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H67" s="5" t="n">
+        <v>18619000</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>30929</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>14709010</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>24434</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -5371,7 +5091,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5379,34 +5099,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H69" s="5" t="n">
+        <v>12832000</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>29635</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>10137280</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>23412</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -5441,7 +5153,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -5449,34 +5161,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H70" s="5" t="n">
+        <v>12832000</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>29635</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>10137280</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>23412</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -5573,7 +5277,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -5581,34 +5285,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H72" s="5" t="n">
+        <v>8116000</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>25684</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>6411640</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>20290</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -5643,7 +5339,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5651,34 +5347,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H73" s="5" t="n">
+        <v>12106000</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>26548</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L73" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>9563740</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>20973</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -5713,7 +5401,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5721,34 +5409,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H74" s="5" t="n">
+        <v>18435000</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>30623</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>14563650</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>24192</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -5783,7 +5463,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -5791,34 +5471,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H75" s="5" t="n">
+        <v>12090000</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>29632</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>9551100</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>23410</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
@@ -5853,7 +5525,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5861,34 +5533,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H76" s="5" t="n">
+        <v>12579000</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>29051</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>9937410</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>22950</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -5923,7 +5587,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5931,34 +5595,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H77" s="5" t="n">
+        <v>12579000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>29051</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>9937410</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>22950</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -6055,7 +5711,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -6063,34 +5719,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H79" s="5" t="n">
+        <v>8093000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>25611</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>6393470</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>20232</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -6125,7 +5773,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -6133,34 +5781,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H80" s="5" t="n">
+        <v>12070000</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>26469</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>9535300</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>20911</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -6257,7 +5897,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -6265,34 +5905,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H82" s="5" t="n">
+        <v>11970000</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>29338</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>9456300</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>23177</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -6327,7 +5959,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6335,34 +5967,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H83" s="5" t="n">
+        <v>12455000</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>28764</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>9839450</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>22724</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -6397,7 +6021,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6405,34 +6029,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H84" s="5" t="n">
+        <v>12455000</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>28764</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>9839450</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>22724</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -6529,7 +6145,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -6537,34 +6153,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H86" s="5" t="n">
+        <v>8068000</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>25532</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>6373720</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>20170</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -6599,7 +6207,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -6607,34 +6215,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H87" s="5" t="n">
+        <v>12033000</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>26388</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L87" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>9506070</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>20847</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
@@ -6801,7 +6401,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -6809,34 +6409,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H90" s="5" t="n">
+        <v>8660000</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>28487</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K90" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L90" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>6841400</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>22505</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -6871,7 +6463,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -6879,34 +6471,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H91" s="5" t="n">
+        <v>8490000</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>28206</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L91" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>6707100</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>22283</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
@@ -6941,7 +6525,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -6949,34 +6533,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H92" s="5" t="n">
+        <v>8490000</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>27928</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>6707100</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>22063</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -7011,7 +6587,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -7019,34 +6595,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H93" s="5" t="n">
+        <v>8490000</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>27928</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L93" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>6707100</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>22063</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
@@ -7143,7 +6711,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -7151,34 +6719,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H95" s="5" t="n">
+        <v>7887000</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>24959</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L95" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>6230730</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>19718</v>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
@@ -7275,7 +6835,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -7283,34 +6843,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H97" s="5" t="n">
+        <v>12427000</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>29035</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>9817330</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>22938</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
@@ -7415,7 +6967,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7423,34 +6975,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H99" s="5" t="n">
+        <v>8608000</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>28316</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>6800320</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>22369</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
@@ -7485,7 +7029,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -7493,34 +7037,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H100" s="5" t="n">
+        <v>8438000</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>28033</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>6666020</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>22146</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N100" s="3" t="inlineStr">
@@ -7555,7 +7091,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7563,34 +7099,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H101" s="5" t="n">
+        <v>8423000</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>27707</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>6654170</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>21889</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -7625,7 +7153,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -7633,34 +7161,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H102" s="5" t="n">
+        <v>8423000</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>27707</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L102" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>6654170</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>21889</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -7757,7 +7277,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7765,34 +7285,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H104" s="5" t="n">
+        <v>7861000</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>24877</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>6210190</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>19652</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N104" s="3" t="inlineStr">
@@ -7889,7 +7401,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -7897,34 +7409,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H106" s="5" t="n">
+        <v>12352000</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>28860</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>9758080</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>22799</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N106" s="3" t="inlineStr">
@@ -8029,7 +7533,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -8037,34 +7541,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H108" s="5" t="n">
+        <v>8556000</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>28145</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L108" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>6759240</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>22234</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N108" s="3" t="inlineStr">
@@ -8099,7 +7595,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -8107,34 +7603,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I109" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H109" s="5" t="n">
+        <v>8389000</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>27870</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K109" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L109" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>6627310</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>22018</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N109" s="3" t="inlineStr">
@@ -8169,7 +7657,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -8177,34 +7665,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H110" s="5" t="n">
+        <v>8355000</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>27484</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L110" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>6600450</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>21712</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
@@ -8239,7 +7719,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8247,34 +7727,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H111" s="5" t="n">
+        <v>8355000</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>27484</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L111" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>6600450</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>21712</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
@@ -8371,7 +7843,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -8379,34 +7851,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H113" s="5" t="n">
+        <v>7838000</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>24804</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L113" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>6192020</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>19595</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N113" s="3" t="inlineStr">
@@ -8503,7 +7967,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -8511,34 +7975,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H115" s="5" t="n">
+        <v>12037000</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>28124</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L115" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>9509230</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>22218</v>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
@@ -8643,7 +8099,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -8651,34 +8107,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H117" s="5" t="n">
+        <v>8507000</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>27984</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L117" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>6720530</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>22107</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -8713,7 +8161,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -8721,34 +8169,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H118" s="5" t="n">
+        <v>8338000</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>27701</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L118" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>6587020</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>21884</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
@@ -8783,7 +8223,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -8791,34 +8231,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H119" s="5" t="n">
+        <v>8290000</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>27270</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L119" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>6549100</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>21543</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N119" s="3" t="inlineStr">
@@ -8853,7 +8285,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -8861,34 +8293,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H120" s="5" t="n">
+        <v>8290000</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>27270</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L120" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>6549100</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>21543</v>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N120" s="3" t="inlineStr">
@@ -8985,7 +8409,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -8993,34 +8417,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H122" s="5" t="n">
+        <v>7816000</v>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>24734</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L122" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>6174640</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>19540</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N122" s="3" t="inlineStr">
@@ -9117,7 +8533,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -9125,34 +8541,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H124" s="5" t="n">
+        <v>11965000</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>27956</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L124" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>9452350</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>22085</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N124" s="3" t="inlineStr">
@@ -9257,7 +8665,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -9265,34 +8673,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H126" s="5" t="n">
+        <v>8455000</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>27812</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L126" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>6679450</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>21972</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
@@ -9327,7 +8727,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -9335,34 +8735,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H127" s="5" t="n">
+        <v>8289000</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>27538</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L127" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>6548310</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>21755</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr">
@@ -9397,7 +8789,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -9405,34 +8797,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H128" s="5" t="n">
+        <v>8223000</v>
+      </c>
+      <c r="I128" s="5" t="n">
+        <v>27049</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L128" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>6496170</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>21369</v>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N128" s="3" t="inlineStr">
@@ -9467,7 +8851,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -9475,34 +8859,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H129" s="5" t="n">
+        <v>8223000</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>27049</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L129" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>6496170</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>21369</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
@@ -9599,7 +8975,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -9607,34 +8983,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I131" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H131" s="5" t="n">
+        <v>7793000</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>24661</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L131" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>6156470</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>19482</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N131" s="3" t="inlineStr">
@@ -9731,7 +9099,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -9739,34 +9107,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H133" s="5" t="n">
+        <v>11894000</v>
+      </c>
+      <c r="I133" s="5" t="n">
+        <v>27790</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L133" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>9396260</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>21954</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr">
@@ -9871,7 +9231,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -9879,34 +9239,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I135" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H135" s="5" t="n">
+        <v>8406000</v>
+      </c>
+      <c r="I135" s="5" t="n">
+        <v>27651</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L135" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>6640740</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>21845</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N135" s="3" t="inlineStr">
@@ -9941,7 +9293,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9949,34 +9301,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H136" s="5" t="n">
+        <v>8240000</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>27375</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K136" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L136" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>6509600</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>21627</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N136" s="3" t="inlineStr">
@@ -10321,7 +9665,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -10329,34 +9673,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H142" s="5" t="n">
+        <v>11823000</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>27624</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L142" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>9340170</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>21823</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
@@ -10461,7 +9797,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -10469,34 +9805,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H144" s="5" t="n">
+        <v>8338000</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>27428</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K144" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L144" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>6587020</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>21668</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N144" s="3" t="inlineStr">
@@ -10531,7 +9859,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -10539,34 +9867,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H145" s="5" t="n">
+        <v>8174000</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>27156</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L145" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>6457460</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>21453</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
@@ -10911,7 +10231,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -10919,34 +10239,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H151" s="5" t="n">
+        <v>11752000</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>27458</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K151" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L151" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>9284080</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>21692</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N151" s="3" t="inlineStr">
@@ -11051,7 +10363,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -11059,34 +10371,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H153" s="5" t="n">
+        <v>8271000</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>27207</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L153" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>6534090</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>21494</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N153" s="3" t="inlineStr">
@@ -11121,7 +10425,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -11129,34 +10433,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H154" s="5" t="n">
+        <v>8109000</v>
+      </c>
+      <c r="I154" s="5" t="n">
+        <v>26940</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L154" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>6406110</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>21283</v>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N154" s="3" t="inlineStr">
@@ -11501,7 +10797,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -11509,34 +10805,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H160" s="5" t="n">
+        <v>11683000</v>
+      </c>
+      <c r="I160" s="5" t="n">
+        <v>27297</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L160" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>9229570</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>21564</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11641,7 +10929,7 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -11649,34 +10937,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I162" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H162" s="5" t="n">
+        <v>8207000</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K162" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L162" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>6483530</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>21327</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N162" s="3" t="inlineStr">
@@ -11711,7 +10991,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -11719,34 +10999,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I163" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H163" s="5" t="n">
+        <v>8045000</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>26728</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L163" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>6355550</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>21115</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N163" s="3" t="inlineStr">
@@ -12091,7 +11363,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -12099,34 +11371,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H169" s="5" t="n">
+        <v>11613000</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>27133</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L169" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>9174270</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>21435</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N169" s="3" t="inlineStr">
@@ -12231,7 +11495,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -12239,34 +11503,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I171" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H171" s="5" t="n">
+        <v>8125000</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>26727</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L171" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>6418750</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>21114</v>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr">
@@ -12301,7 +11557,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -12309,34 +11565,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H172" s="5" t="n">
+        <v>7965000</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>26462</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L172" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>6292350</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>20905</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N172" s="3" t="inlineStr">
@@ -12681,7 +11929,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12689,34 +11937,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H178" s="5" t="n">
+        <v>11544000</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>26972</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L178" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>9119760</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>21308</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -12821,7 +12061,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -12829,34 +12069,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H180" s="5" t="n">
+        <v>8045000</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>26464</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L180" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>6355550</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>20906</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N180" s="3" t="inlineStr">
@@ -12891,7 +12123,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -12899,34 +12131,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I181" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H181" s="5" t="n">
+        <v>7887000</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>26203</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K181" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L181" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>6230730</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>20700</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr">
@@ -13271,7 +12495,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -13279,34 +12503,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H187" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I187" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H187" s="5" t="n">
+        <v>11475000</v>
+      </c>
+      <c r="I187" s="5" t="n">
+        <v>26811</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K187" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L187" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>9065250</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>21180</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -13411,7 +12627,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -13419,34 +12635,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H189" s="5" t="n">
+        <v>7888000</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>25947</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L189" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>6231520</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>20498</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
@@ -13481,7 +12689,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -13489,34 +12697,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H190" s="5" t="n">
+        <v>7732000</v>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>25688</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L190" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>6108280</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>20293</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N190" s="3" t="inlineStr">
@@ -13675,7 +12875,7 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -13685,12 +12885,12 @@
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J193" s="3" t="inlineStr">
@@ -13700,12 +12900,12 @@
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M193" s="3" t="inlineStr">
@@ -13715,7 +12915,7 @@
       </c>
       <c r="N193" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13745,7 +12945,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -13755,12 +12955,12 @@
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J194" s="3" t="inlineStr">
@@ -13770,12 +12970,12 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
@@ -13785,7 +12985,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13877,7 +13077,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -13885,34 +13085,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H196" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I196" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H196" s="5" t="n">
+        <v>11406000</v>
+      </c>
+      <c r="I196" s="5" t="n">
+        <v>26650</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K196" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L196" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>9010740</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>21053</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N196" s="3" t="inlineStr">
@@ -13998,27 +13190,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>140</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -14117,20 +13309,20 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1465呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
+$5860万
+$40,000/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1393呎 (2房)
-招标单位
--
-(在售)</t>
+$5851万
+$42,000/呎
+(26年-09月-19日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -14163,15 +13355,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 796呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
+$3143万
+$39,487/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 -
@@ -14179,7 +13371,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 -
@@ -14198,12 +13390,12 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
-招标单位
--
-(在售)</t>
+$2196万
+$36,000/呎
+(26年-09月-19日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -14222,7 +13414,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 -
@@ -14230,7 +13422,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 -
@@ -14249,20 +13441,20 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
+$2013万
+$33,000/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 767呎 (3房)
-招标单位
--
-(在售)</t>
+$2454万
+$32,000/呎
+(26年-09月-19日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -14273,7 +13465,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 -
@@ -14281,7 +13473,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 -
@@ -14300,31 +13492,31 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
+$1922万
+$31,500/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 767呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
+$2301万
+$30,000/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
+$2557万
+$31,997/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 -
@@ -14332,7 +13524,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 -
@@ -14351,31 +13543,31 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
+$1830万
+$30,000/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 729呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
+$2114万
+$29,000/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 792呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
+$2455万
+$31,000/呎
+(26年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 -
@@ -14383,7 +13575,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 -
@@ -14402,7 +13594,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 -
@@ -14410,23 +13602,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
+$1229万
+$26,947/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
+$840万
+$26,592/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 450呎 (2房)
 -
@@ -14434,23 +13626,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="inlineStr">
+$1438万
+$33,199/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="inlineStr">
+$1438万
+$33,199/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -14467,31 +13659,31 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+$1937万
+$32,183/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+$1225万
+$26,868/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
+$838万
+$26,513/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 -
@@ -14499,23 +13691,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
+$1466万
+$33,850/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
+$1402万
+$32,390/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -14532,31 +13724,31 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+$1909万
+$31,708/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
+$1222万
+$26,789/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
+$835万
+$26,430/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 -
@@ -14564,23 +13756,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="inlineStr">
+$1368万
+$31,600/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
+$1368万
+$31,600/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -14597,31 +13789,31 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
+$1881万
+$31,239/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
+$1218万
+$26,708/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
+$816万
+$25,835/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1284万
@@ -14629,23 +13821,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
+$1335万
+$30,831/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
+$1335万
+$30,831/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -14662,31 +13854,31 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
+$1862万
+$30,929/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
+$1214万
+$26,627/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
+$814万
+$25,759/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1272万
@@ -14694,23 +13886,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
+$1309万
+$30,226/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
+$1309万
+$30,226/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -14727,31 +13919,31 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
+$1844万
+$30,623/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
+$1211万
+$26,548/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
+$812万
+$25,684/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1259万
@@ -14759,23 +13951,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
+$1283万
+$29,635/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
+$1283万
+$29,635/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 -
@@ -14792,7 +13984,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1825万
@@ -14800,23 +13992,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
+$1207万
+$26,469/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
+$809万
+$25,611/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1247万
@@ -14824,28 +14016,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
+$1258万
+$29,051/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
+$1258万
+$29,051/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$1209万
+$29,632/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr"/>
@@ -14857,7 +14049,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1807万
@@ -14865,23 +14057,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
+$1203万
+$26,388/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
+$807万
+$25,532/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1234万
@@ -14889,28 +14081,28 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="inlineStr">
+$1246万
+$28,764/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
+$1246万
+$28,764/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
--
--
-(待售)</t>
+$1197万
+$29,338/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr"/>
@@ -14922,15 +14114,15 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
+$1243万
+$29,035/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1168万
@@ -14938,15 +14130,15 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
+$789万
+$24,959/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1222万
@@ -14954,39 +14146,39 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="inlineStr">
+$849万
+$27,928/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
+$849万
+$27,928/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
+$849万
+$28,206/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="22" t="inlineStr">
+$866万
+$28,487/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15001,15 +14193,15 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
+$1235万
+$28,860/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1162万
@@ -15017,15 +14209,15 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
+$786万
+$24,877/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1215万
@@ -15033,39 +14225,39 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="22" t="inlineStr">
+$842万
+$27,707/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
+$842万
+$27,707/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="22" t="inlineStr">
+$844万
+$28,033/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="22" t="inlineStr">
+$861万
+$28,316/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15080,15 +14272,15 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
+$1204万
+$28,124/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1155万
@@ -15096,15 +14288,15 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="inlineStr">
+$784万
+$24,804/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1208万
@@ -15112,39 +14304,39 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="inlineStr">
+$836万
+$27,484/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
+$836万
+$27,484/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
+$839万
+$27,870/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="22" t="inlineStr">
+$856万
+$28,145/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15159,15 +14351,15 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
+$1196万
+$27,956/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1148万
@@ -15175,15 +14367,15 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
+$782万
+$24,734/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1200万
@@ -15191,39 +14383,39 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="inlineStr">
+$829万
+$27,270/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
+$829万
+$27,270/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
+$834万
+$27,701/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="22" t="inlineStr">
+$851万
+$27,984/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15238,15 +14430,15 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
+$1189万
+$27,790/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1141万
@@ -15254,15 +14446,15 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="23" t="inlineStr">
+$779万
+$24,661/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1193万
@@ -15270,39 +14462,39 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
+$822万
+$27,049/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
+$822万
+$27,049/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
+$829万
+$27,538/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="22" t="inlineStr">
+$846万
+$27,812/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15317,15 +14509,15 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
+$1182万
+$27,624/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1134万
@@ -15333,7 +14525,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $777万
@@ -15341,7 +14533,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1186万
@@ -15349,7 +14541,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $816万
@@ -15357,7 +14549,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $816万
@@ -15365,23 +14557,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
+$824万
+$27,375/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="22" t="inlineStr">
+$841万
+$27,651/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J25" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15396,15 +14588,15 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
+$1175万
+$27,458/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1127万
@@ -15412,7 +14604,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $772万
@@ -15420,7 +14612,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1177万
@@ -15428,7 +14620,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $809万
@@ -15436,7 +14628,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G26" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $809万
@@ -15444,23 +14636,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="22" t="inlineStr">
+$817万
+$27,156/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="22" t="inlineStr">
+$834万
+$27,428/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15475,15 +14667,15 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
+$1168万
+$27,297/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1121万
@@ -15491,7 +14683,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $768万
@@ -15499,7 +14691,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1167万
@@ -15507,7 +14699,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $803万
@@ -15515,7 +14707,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="G27" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $803万
@@ -15523,23 +14715,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="22" t="inlineStr">
+$811万
+$26,940/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="22" t="inlineStr">
+$827万
+$27,207/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J27" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15554,15 +14746,15 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
+$1161万
+$27,133/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1114万
@@ -15570,7 +14762,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $763万
@@ -15578,7 +14770,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1158万
@@ -15586,7 +14778,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $796万
@@ -15594,7 +14786,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $796万
@@ -15602,23 +14794,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr">
+$804万
+$26,728/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="22" t="inlineStr">
+$821万
+$26,997/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15633,15 +14825,15 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
+$1154万
+$26,972/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1107万
@@ -15649,7 +14841,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $758万
@@ -15657,7 +14849,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1147万
@@ -15665,7 +14857,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
+      <c r="F29" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $789万
@@ -15673,7 +14865,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr">
+      <c r="G29" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $789万
@@ -15681,23 +14873,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="22" t="inlineStr">
+$796万
+$26,462/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="22" t="inlineStr">
+$812万
+$26,727/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15712,15 +14904,15 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
+$1148万
+$26,811/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1096万
@@ -15728,7 +14920,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $754万
@@ -15736,7 +14928,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1135万
@@ -15744,7 +14936,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $781万
@@ -15752,7 +14944,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $781万
@@ -15760,23 +14952,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H30" s="22" t="inlineStr">
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="22" t="inlineStr">
+$789万
+$26,203/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="22" t="inlineStr">
+$804万
+$26,464/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -
@@ -15791,15 +14983,15 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
+$1141万
+$26,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1086万
@@ -15807,23 +14999,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 413呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>D | 413呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>E | 305呎 (1房)
 $768万
@@ -15831,7 +15023,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr">
+      <c r="G31" s="24" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $766万
@@ -15839,23 +15031,23 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I31" s="22" t="inlineStr">
+$773万
+$25,688/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J31" s="22" t="inlineStr">
+$789万
+$25,947/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 -

--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,11 +130,6 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -212,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -281,9 +276,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1933,38 +1925,30 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>27163500</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>33997</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K20" s="5" t="n">
+        <v>27163500</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>33997</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1957,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2833,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2911,7 +2895,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3043,7 +3027,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3105,7 +3089,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3307,7 +3291,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3369,7 +3353,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3501,7 +3485,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3563,7 +3547,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3625,7 +3609,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3757,7 +3741,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3819,7 +3803,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3951,7 +3935,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -4013,7 +3997,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4075,7 +4059,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4207,7 +4191,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4269,7 +4253,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -4331,7 +4315,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4393,7 +4377,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4455,7 +4439,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4517,7 +4501,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4649,7 +4633,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4711,7 +4695,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4773,7 +4757,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4835,7 +4819,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -4897,7 +4881,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -4959,7 +4943,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -5091,7 +5075,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5153,7 +5137,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -5215,7 +5199,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -5277,7 +5261,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -5339,7 +5323,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5401,7 +5385,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -5463,7 +5447,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -5525,7 +5509,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5587,7 +5571,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5649,7 +5633,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -5711,7 +5695,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -5773,7 +5757,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -5835,7 +5819,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -5897,7 +5881,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -5959,7 +5943,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6021,7 +6005,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6083,7 +6067,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6145,7 +6129,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -6207,7 +6191,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -6269,7 +6253,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6401,7 +6385,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -6463,7 +6447,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -6525,7 +6509,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -6587,7 +6571,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -6649,7 +6633,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -6711,7 +6695,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -6773,7 +6757,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -6835,7 +6819,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
@@ -6967,7 +6951,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7029,7 +7013,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -7091,7 +7075,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
@@ -7153,7 +7137,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -7215,7 +7199,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -7277,7 +7261,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7339,7 +7323,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7401,7 +7385,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -7533,7 +7517,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -7595,7 +7579,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -7657,7 +7641,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -7719,7 +7703,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -7781,7 +7765,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -7843,7 +7827,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -7905,7 +7889,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -7967,7 +7951,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -8099,7 +8083,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -8161,7 +8145,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -8223,7 +8207,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -8285,7 +8269,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -8347,7 +8331,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -8409,7 +8393,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -8471,7 +8455,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -8533,7 +8517,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -8665,7 +8649,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -8727,7 +8711,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -8789,7 +8773,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -8851,7 +8835,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -8913,7 +8897,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -8975,7 +8959,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -9037,7 +9021,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -9099,7 +9083,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -9231,7 +9215,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -9293,7 +9277,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9355,7 +9339,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
@@ -9417,7 +9401,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -9479,7 +9463,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -9541,7 +9525,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -9603,7 +9587,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -9665,7 +9649,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -9797,7 +9781,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -9859,7 +9843,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -9921,7 +9905,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -9983,7 +9967,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -10045,7 +10029,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -10107,7 +10091,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -10169,7 +10153,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -10231,7 +10215,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -10363,7 +10347,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -10425,7 +10409,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -10487,7 +10471,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -10549,7 +10533,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -10611,7 +10595,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -10673,7 +10657,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -10735,7 +10719,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -10797,7 +10781,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -10929,7 +10913,7 @@
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -10991,7 +10975,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -11053,7 +11037,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -11115,7 +11099,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -11177,7 +11161,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -11239,7 +11223,7 @@
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
@@ -11301,7 +11285,7 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -11363,7 +11347,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -11495,7 +11479,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -11557,7 +11541,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -11619,7 +11603,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -11681,7 +11665,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -11743,7 +11727,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -11805,7 +11789,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -11867,7 +11851,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -11929,7 +11913,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12061,7 +12045,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -12123,7 +12107,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -12185,7 +12169,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -12247,7 +12231,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -12309,7 +12293,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -12371,7 +12355,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -12433,7 +12417,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -12495,7 +12479,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -12627,7 +12611,7 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -12689,7 +12673,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -12751,7 +12735,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -12813,7 +12797,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -12945,38 +12929,30 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H194" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I194" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="n">
+        <v>8310000</v>
+      </c>
+      <c r="I194" s="5" t="n">
+        <v>30000</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K194" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L194" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K194" s="5" t="n">
+        <v>8310000</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>30000</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -12985,7 +12961,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13015,7 +12991,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -13077,7 +13053,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -13190,17 +13166,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>148</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -13457,12 +13433,12 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
-招标单位
--
-(在售)</t>
+$2716万
+$33,997/呎
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -13602,20 +13578,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $1229万
 $26,947/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $840万
 $26,592/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -13626,20 +13602,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1438万
 $33,199/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G12" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1438万
 $33,199/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -13659,28 +13635,28 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1937万
 $32,183/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $1225万
 $26,868/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $838万
 $26,513/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -13691,20 +13667,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1466万
 $33,850/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1402万
 $32,390/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
@@ -13724,28 +13700,28 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1909万
 $31,708/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $1222万
 $26,789/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $835万
 $26,430/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -13756,20 +13732,20 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1368万
 $31,600/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G14" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1368万
 $31,600/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -13789,52 +13765,52 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1881万
 $31,239/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $1218万
 $26,708/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $816万
 $25,835/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1284万
 $28,481/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1335万
 $30,831/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1335万
 $30,831/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -13854,52 +13830,52 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1862万
 $30,929/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $1214万
 $26,627/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $814万
 $25,759/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1272万
 $28,197/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1309万
 $30,226/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1309万
 $30,226/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -13919,52 +13895,52 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1844万
 $30,623/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $1211万
 $26,548/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $812万
 $25,684/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1259万
 $27,916/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1283万
 $29,635/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1283万
 $29,635/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -13984,60 +13960,60 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1825万
 $30,319/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $1207万
 $26,469/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $809万
 $25,611/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1247万
 $27,641/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1258万
 $29,051/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1258万
 $29,051/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1209万
 $29,632/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr"/>
@@ -14049,60 +14025,60 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1807万
 $30,022/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $1203万
 $26,388/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $807万
 $25,532/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1234万
 $27,370/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1246万
 $28,764/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G19" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1246万
 $28,764/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1197万
 $29,338/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr"/>
@@ -14114,68 +14090,68 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1243万
 $29,035/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1168万
 $25,792/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $789万
 $24,959/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1222万
 $27,098/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $849万
 $27,928/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G20" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $849万
 $27,928/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H20" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $849万
 $28,206/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $866万
 $28,487/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
@@ -14193,68 +14169,68 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1235万
 $28,860/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1162万
 $25,642/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $786万
 $24,877/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1215万
 $26,938/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F21" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $842万
 $27,707/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G21" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $842万
 $27,707/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $844万
 $28,033/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I21" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $861万
 $28,316/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
@@ -14272,68 +14248,68 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1204万
 $28,124/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1155万
 $25,488/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $784万
 $24,804/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1208万
 $26,774/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $836万
 $27,484/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $836万
 $27,484/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $839万
 $27,870/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I22" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $856万
 $28,145/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -14351,68 +14327,68 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1196万
 $27,956/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1148万
 $25,333/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D23" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $782万
 $24,734/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1200万
 $26,614/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $829万
 $27,270/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G23" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $829万
 $27,270/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $834万
 $27,701/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I23" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $851万
 $27,984/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
@@ -14430,68 +14406,68 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1189万
 $27,790/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1141万
 $25,185/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D24" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $779万
 $24,661/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1193万
 $26,457/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $822万
 $27,049/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G24" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $822万
 $27,049/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $829万
 $27,538/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I24" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $846万
 $27,812/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
@@ -14509,68 +14485,68 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1182万
 $27,624/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C25" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1134万
 $25,035/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $777万
 $24,582/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1186万
 $26,299/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $816万
 $26,839/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $816万
 $26,839/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H25" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $824万
 $27,375/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $841万
 $27,651/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
@@ -14588,68 +14564,68 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1175万
 $27,458/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1127万
 $24,885/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $772万
 $24,437/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1177万
 $26,089/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $809万
 $26,625/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G26" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $809万
 $26,625/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H26" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $817万
 $27,156/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I26" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $834万
 $27,428/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -14667,68 +14643,68 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1168万
 $27,297/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1121万
 $24,740/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $768万
 $24,291/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1167万
 $25,882/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $803万
 $26,414/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $803万
 $26,414/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $811万
 $26,940/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I27" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $827万
 $27,207/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
@@ -14746,68 +14722,68 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1161万
 $27,133/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1114万
 $24,592/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D28" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $763万
 $24,149/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1158万
 $25,676/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F28" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $796万
 $26,201/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G28" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $796万
 $26,201/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H28" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $804万
 $26,728/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I28" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $821万
 $26,997/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
@@ -14825,68 +14801,68 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B29" s="24" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1154万
 $26,972/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1107万
 $24,444/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $758万
 $24,003/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E29" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1147万
 $25,424/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F29" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $789万
 $25,947/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G29" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $789万
 $25,947/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H29" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $796万
 $26,462/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I29" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $812万
 $26,727/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -14904,68 +14880,68 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1148万
 $26,811/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1096万
 $24,201/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $754万
 $23,861/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1135万
 $25,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $781万
 $25,688/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G30" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $781万
 $25,688/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H30" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $789万
 $26,203/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I30" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $804万
 $26,464/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -14983,28 +14959,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $1141万
 $26,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $1086万
 $23,962/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
-招标单位
--
-(在售)</t>
+$831万
+$30,000/呎
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -15015,36 +14991,36 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F31" s="24" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 305呎 (1房)
 $768万
 $25,187/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G31" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $766万
 $25,181/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H31" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $773万
 $25,688/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I31" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $789万
 $25,947/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">

--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,11 +125,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -207,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -273,9 +268,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -658,7 +650,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1093,34 +1085,34 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>17098000</v>
+        <v>13336000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>39579</v>
+        <v>30870</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>13507420</v>
+        <v>13336000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>31267</v>
+        <v>30870</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1155,34 +1147,34 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>15823000</v>
+        <v>13062000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>40676</v>
+        <v>33578</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>12500170</v>
+        <v>13062000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>32134</v>
+        <v>33578</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1222,7 +1214,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1419,34 +1411,34 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>16682000</v>
+        <v>13011000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>38616</v>
+        <v>30118</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>13178780</v>
+        <v>13011000</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>30506</v>
+        <v>30118</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1481,34 +1473,34 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>15437000</v>
+        <v>12689000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>39684</v>
+        <v>32620</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>12195230</v>
+        <v>12689000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>31350</v>
+        <v>32620</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1737,34 +1729,34 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>16274000</v>
+        <v>12693000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>37671</v>
+        <v>29382</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>12856460</v>
+        <v>12693000</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>29760</v>
+        <v>29382</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -1799,34 +1791,34 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>15061000</v>
+        <v>12375000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>38717</v>
+        <v>31812</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>11898190</v>
+        <v>12375000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>30587</v>
+        <v>31812</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -1990,7 +1982,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2047,34 +2039,34 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>15878000</v>
+        <v>12343000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>36755</v>
+        <v>28572</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>12543620</v>
+        <v>12343000</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>29036</v>
+        <v>28572</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2109,34 +2101,34 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>14694000</v>
+        <v>11458000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>37774</v>
+        <v>29455</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>11608260</v>
+        <v>11458000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>29841</v>
+        <v>29455</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2357,34 +2349,34 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>15490000</v>
+        <v>12037000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>35856</v>
+        <v>27863</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>12237100</v>
+        <v>12037000</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>28327</v>
+        <v>27863</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -2419,34 +2411,34 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>14336000</v>
+        <v>11970000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>36853</v>
+        <v>30771</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>11325440</v>
+        <v>11970000</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>29114</v>
+        <v>30771</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -2667,34 +2659,34 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>14494000</v>
+        <v>11250000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>35525</v>
+        <v>27574</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>11450260</v>
+        <v>11250000</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>28064</v>
+        <v>27574</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2853,34 +2845,34 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>14964000</v>
+        <v>12294000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>33253</v>
+        <v>27320</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>11821560</v>
+        <v>12294000</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>26270</v>
+        <v>27320</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -3039,34 +3031,34 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>21118000</v>
+        <v>16472000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>35080</v>
+        <v>27362</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>16683220</v>
+        <v>16472000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>27713</v>
+        <v>27362</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -3101,34 +3093,34 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
-        <v>14141000</v>
+        <v>11607000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>34659</v>
+        <v>28449</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>11171390</v>
+        <v>11607000</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>27381</v>
+        <v>28449</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -3287,34 +3279,34 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>14490000</v>
+        <v>11247000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>32129</v>
+        <v>24938</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>11447100</v>
+        <v>11247000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>25382</v>
+        <v>24938</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -3535,34 +3527,34 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>13795000</v>
+        <v>11318000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>33811</v>
+        <v>27740</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>10898050</v>
+        <v>11318000</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>26711</v>
+        <v>27740</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -3721,34 +3713,34 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>13999000</v>
+        <v>11689000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>31040</v>
+        <v>25918</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>11059210</v>
+        <v>11689000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>24522</v>
+        <v>25918</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -3969,34 +3961,34 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>13459000</v>
+        <v>10482000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>32988</v>
+        <v>25691</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>10632610</v>
+        <v>10482000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>26060</v>
+        <v>25691</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -4403,34 +4395,34 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>13195000</v>
+        <v>10424000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>32341</v>
+        <v>25549</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>10424050</v>
+        <v>10424000</v>
       </c>
       <c r="L61" s="5" t="n">
         <v>25549</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -4837,34 +4829,34 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>12937000</v>
+        <v>10220000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>31708</v>
+        <v>25049</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="5" t="n">
-        <v>10220230</v>
+        <v>10220000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>25050</v>
+        <v>25049</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -6139,34 +6131,34 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>9540000</v>
+        <v>7441000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>31589</v>
+        <v>24639</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="5" t="n">
-        <v>7536600</v>
+        <v>7441000</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>24956</v>
+        <v>24639</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -6697,34 +6689,34 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>9483000</v>
+        <v>7491000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>31401</v>
+        <v>24805</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="5" t="n">
-        <v>7491570</v>
+        <v>7491000</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>24807</v>
+        <v>24805</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
@@ -7255,34 +7247,34 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>9427000</v>
+        <v>7447000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>31215</v>
+        <v>24659</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="5" t="n">
-        <v>7447330</v>
+        <v>7447000</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>24660</v>
+        <v>24659</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
@@ -7813,34 +7805,34 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>9370000</v>
+        <v>7823000</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>31026</v>
+        <v>25904</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="5" t="n">
-        <v>7402300</v>
+        <v>7823000</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>24511</v>
+        <v>25904</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N116" s="3" t="inlineStr">
@@ -8371,34 +8363,34 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
-        <v>9314000</v>
+        <v>7777000</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>30841</v>
+        <v>25752</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="5" t="n">
-        <v>7358060</v>
+        <v>7777000</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>24364</v>
+        <v>25752</v>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
@@ -8929,34 +8921,34 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
-        <v>9259000</v>
+        <v>7731000</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>30659</v>
+        <v>25599</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="5" t="n">
-        <v>7314610</v>
+        <v>7731000</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>24221</v>
+        <v>25599</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N134" s="3" t="inlineStr">
@@ -9487,34 +9479,34 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
-        <v>9184000</v>
+        <v>7668000</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>30411</v>
+        <v>25391</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>7255360</v>
+        <v>7668000</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>24024</v>
+        <v>25391</v>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N143" s="3" t="inlineStr">
@@ -10045,34 +10037,34 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
-        <v>9113000</v>
+        <v>7108000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>30175</v>
+        <v>23536</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K152" s="5" t="n">
-        <v>7199270</v>
+        <v>7108000</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>23839</v>
+        <v>23536</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N152" s="3" t="inlineStr">
@@ -10603,34 +10595,34 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
-        <v>9040000</v>
+        <v>7548000</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>29934</v>
+        <v>24993</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="5" t="n">
-        <v>7141600</v>
+        <v>7548000</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>23648</v>
+        <v>24993</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N161" s="3" t="inlineStr">
@@ -11161,34 +11153,34 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
-        <v>8950000</v>
+        <v>7070000</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>29636</v>
+        <v>23411</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K170" s="5" t="n">
-        <v>7070500</v>
+        <v>7070000</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>23412</v>
+        <v>23411</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N170" s="3" t="inlineStr">
@@ -11719,34 +11711,34 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
-        <v>8861000</v>
+        <v>7000000</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>29341</v>
+        <v>23179</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K179" s="5" t="n">
-        <v>7000190</v>
+        <v>7000000</v>
       </c>
       <c r="L179" s="5" t="n">
         <v>23179</v>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr">
@@ -12277,34 +12269,34 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
-        <v>8689000</v>
+        <v>6864000</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>28772</v>
+        <v>22728</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K188" s="5" t="n">
-        <v>6864310</v>
+        <v>6864000</v>
       </c>
       <c r="L188" s="5" t="n">
-        <v>22730</v>
+        <v>22728</v>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N188" s="3" t="inlineStr">
@@ -12587,38 +12579,30 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H193" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I193" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="n">
+        <v>12390000</v>
+      </c>
+      <c r="I193" s="5" t="n">
+        <v>30000</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K193" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L193" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K193" s="5" t="n">
+        <v>12390000</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>30000</v>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
@@ -12627,7 +12611,7 @@
       </c>
       <c r="N193" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12894,17 +12878,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>189</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -13064,23 +13048,23 @@
           <t>C | 796呎 (3房)
 $3143万
 $39,487/呎
-(26年-09月-19日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
-$1582万
-$40,676/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
+$1306万
+$33,578/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
-$1710万
-$39,579/呎
-(已定价未售)</t>
+$1334万
+$30,870/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr"/>
@@ -13118,20 +13102,20 @@
 (26年-09月-25日)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
-$1544万
-$39,684/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
+$1269万
+$32,620/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
-$1668万
-$38,616/呎
-(已定价未售)</t>
+$1301万
+$30,118/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr"/>
@@ -13150,7 +13134,7 @@
           <t>A | 610呎 (3房)
 $2013万
 $33,000/呎
-(26年-09月-19日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -13169,20 +13153,20 @@
 (26年-09月-23日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
-$1506万
-$38,717/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
+$1238万
+$31,812/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
-$1627万
-$37,671/呎
-(已定价未售)</t>
+$1269万
+$29,382/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr"/>
@@ -13220,20 +13204,20 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
-$1469万
-$37,774/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
+$1146万
+$29,455/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
-$1588万
-$36,755/呎
-(已定价未售)</t>
+$1234万
+$28,572/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr"/>
@@ -13271,20 +13255,20 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
-$1434万
-$36,853/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
+$1197万
+$30,771/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
-$1549万
-$35,856/呎
-(已定价未售)</t>
+$1204万
+$27,863/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr"/>
@@ -13298,12 +13282,12 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
-$2112万
-$35,080/呎
-(已定价未售)</t>
+$1647万
+$27,362/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -13322,12 +13306,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 450呎 (2房)
-$1496万
-$33,253/呎
-(已定价未售)</t>
+$1229万
+$27,320/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -13346,12 +13330,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
-$1449万
-$35,525/呎
-(已定价未售)</t>
+$1125万
+$27,574/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr"/>
@@ -13387,12 +13371,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
-$1449万
-$32,129/呎
-(已定价未售)</t>
+$1125万
+$24,938/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -13411,12 +13395,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
-$1414万
-$34,659/呎
-(已定价未售)</t>
+$1161万
+$28,449/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr"/>
@@ -13452,12 +13436,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
-$1400万
-$31,040/呎
-(已定价未售)</t>
+$1169万
+$25,918/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -13476,12 +13460,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
-$1380万
-$33,811/呎
-(已定价未售)</t>
+$1132万
+$27,740/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr"/>
@@ -13541,12 +13525,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
-$1346万
-$32,988/呎
-(已定价未售)</t>
+$1048万
+$25,691/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr"/>
@@ -13606,12 +13590,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
-$1320万
-$32,341/呎
-(已定价未售)</t>
+$1042万
+$25,549/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr"/>
@@ -13671,12 +13655,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
-$1294万
-$31,708/呎
-(已定价未售)</t>
+$1022万
+$25,049/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr"/>
@@ -13882,12 +13866,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J20" s="23" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$954万
-$31,589/呎
-(已定价未售)</t>
+$744万
+$24,639/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -13961,12 +13945,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J21" s="23" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$948万
-$31,401/呎
-(已定价未售)</t>
+$749万
+$24,805/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -14040,12 +14024,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J22" s="23" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$943万
-$31,215/呎
-(已定价未售)</t>
+$745万
+$24,659/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -14119,12 +14103,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J23" s="23" t="inlineStr">
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$937万
-$31,026/呎
-(已定价未售)</t>
+$782万
+$25,904/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -14198,12 +14182,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J24" s="23" t="inlineStr">
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$931万
-$30,841/呎
-(已定价未售)</t>
+$778万
+$25,752/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -14277,12 +14261,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J25" s="23" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$926万
-$30,659/呎
-(已定价未售)</t>
+$773万
+$25,599/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -14356,12 +14340,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J26" s="23" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$918万
-$30,411/呎
-(已定价未售)</t>
+$767万
+$25,391/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14419,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J27" s="23" t="inlineStr">
+      <c r="J27" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$911万
-$30,175/呎
-(已定价未售)</t>
+$711万
+$23,536/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -14514,12 +14498,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J28" s="23" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$904万
-$29,934/呎
-(已定价未售)</t>
+$755万
+$24,993/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -14593,12 +14577,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J29" s="23" t="inlineStr">
+      <c r="J29" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$895万
-$29,636/呎
-(已定价未售)</t>
+$707万
+$23,411/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -14672,12 +14656,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J30" s="23" t="inlineStr">
+      <c r="J30" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$886万
-$29,341/呎
-(已定价未售)</t>
+$700万
+$23,179/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -14711,12 +14695,12 @@
 (26年-09月-23日)</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 413呎 (2房)
-招标单位
--
-(在售)</t>
+$1239万
+$30,000/呎
+(26年-10月-01日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -14751,12 +14735,12 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J31" s="23" t="inlineStr">
+      <c r="J31" s="21" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$869万
-$28,772/呎
-(已定价未售)</t>
+$686万
+$22,728/呎
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>

--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -264,10 +264,10 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -829,30 +829,38 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>56000000</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>50000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K4" s="5" t="n">
-        <v>56000000</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>50000</v>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -861,7 +869,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1680,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -2230,7 +2238,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2292,7 +2300,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2540,7 +2548,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -12878,7 +12886,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -12888,7 +12896,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>188</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -12968,12 +12976,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 1120呎 (3房)
-$5600万
-$50,000/呎
-(26年-09月-26日)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -12984,12 +12992,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr"/>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="22" t="inlineStr"/>
-      <c r="H5" s="22" t="inlineStr"/>
-      <c r="I5" s="22" t="inlineStr"/>
-      <c r="J5" s="22" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -12997,7 +13005,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1465呎 (2房)
 $5860万
@@ -13005,7 +13013,7 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1393呎 (2房)
 $5851万
@@ -13013,13 +13021,13 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr"/>
-      <c r="E6" s="22" t="inlineStr"/>
-      <c r="F6" s="22" t="inlineStr"/>
-      <c r="G6" s="22" t="inlineStr"/>
-      <c r="H6" s="22" t="inlineStr"/>
-      <c r="I6" s="22" t="inlineStr"/>
-      <c r="J6" s="22" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -13043,7 +13051,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 796呎 (3房)
 $3143万
@@ -13051,7 +13059,7 @@
 (26年-10月-05日)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $1306万
@@ -13059,7 +13067,7 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 $1334万
@@ -13067,10 +13075,10 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr"/>
-      <c r="H7" s="22" t="inlineStr"/>
-      <c r="I7" s="22" t="inlineStr"/>
-      <c r="J7" s="22" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -13078,12 +13086,12 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
 $2196万
 $36,000/呎
-(26年-09月-19日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -13094,7 +13102,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
 $3196万
@@ -13102,7 +13110,7 @@
 (26年-09月-25日)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $1269万
@@ -13110,7 +13118,7 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 $1301万
@@ -13118,10 +13126,10 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr"/>
-      <c r="H8" s="22" t="inlineStr"/>
-      <c r="I8" s="22" t="inlineStr"/>
-      <c r="J8" s="22" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+      <c r="H8" s="21" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -13129,7 +13137,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
 $2013万
@@ -13137,7 +13145,7 @@
 (26年-10月-05日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 767呎 (3房)
 $2454万
@@ -13145,7 +13153,7 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
 $2716万
@@ -13153,7 +13161,7 @@
 (26年-09月-23日)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $1238万
@@ -13161,7 +13169,7 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 $1269万
@@ -13169,10 +13177,10 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr"/>
-      <c r="H9" s="22" t="inlineStr"/>
-      <c r="I9" s="22" t="inlineStr"/>
-      <c r="J9" s="22" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
+      <c r="H9" s="21" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -13180,23 +13188,23 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
 $1922万
 $31,500/呎
-(26年-09月-19日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
+(26年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 767呎 (3房)
 $2301万
 $30,000/呎
-(26年-09月-19日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
+(26年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
 $2557万
@@ -13204,7 +13212,7 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $1146万
@@ -13212,7 +13220,7 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 $1234万
@@ -13220,10 +13228,10 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr"/>
-      <c r="H10" s="22" t="inlineStr"/>
-      <c r="I10" s="22" t="inlineStr"/>
-      <c r="J10" s="22" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+      <c r="H10" s="21" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -13231,7 +13239,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 610呎 (3房)
 $1830万
@@ -13239,15 +13247,15 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 729呎 (3房)
 $2114万
 $29,000/呎
-(26年-09月-19日)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
+(26年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 792呎 (3房)
 $2455万
@@ -13255,7 +13263,7 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 389呎 (2房)
 $1197万
@@ -13263,7 +13271,7 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 432呎 (2房)
 $1204万
@@ -13271,10 +13279,10 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr"/>
-      <c r="H11" s="22" t="inlineStr"/>
-      <c r="I11" s="22" t="inlineStr"/>
-      <c r="J11" s="22" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
+      <c r="H11" s="21" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -13282,7 +13290,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1647万
@@ -13290,7 +13298,7 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $951万
@@ -13298,7 +13306,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $664万
@@ -13306,7 +13314,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 450呎 (2房)
 $1229万
@@ -13314,7 +13322,7 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1121万
@@ -13322,7 +13330,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1186万
@@ -13330,7 +13338,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1125万
@@ -13338,8 +13346,8 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr"/>
-      <c r="J12" s="22" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -13347,7 +13355,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1511万
@@ -13355,7 +13363,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $948万
@@ -13363,7 +13371,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $662万
@@ -13371,7 +13379,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1125万
@@ -13379,7 +13387,7 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1158万
@@ -13387,7 +13395,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1108万
@@ -13395,7 +13403,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1161万
@@ -13403,8 +13411,8 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr"/>
-      <c r="J13" s="22" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -13412,7 +13420,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1489万
@@ -13420,7 +13428,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $950万
@@ -13428,7 +13436,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $660万
@@ -13436,7 +13444,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1169万
@@ -13444,7 +13452,7 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1122万
@@ -13452,7 +13460,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1122万
@@ -13460,7 +13468,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1132万
@@ -13468,8 +13476,8 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr"/>
-      <c r="J14" s="22" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -13477,7 +13485,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1466万
@@ -13485,7 +13493,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $1002万
@@ -13493,7 +13501,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $645万
@@ -13501,7 +13509,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $995万
@@ -13509,7 +13517,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1035万
@@ -13517,7 +13525,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1095万
@@ -13525,7 +13533,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1048万
@@ -13533,8 +13541,8 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr"/>
-      <c r="J15" s="22" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -13542,7 +13550,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1451万
@@ -13550,7 +13558,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $939万
@@ -13558,7 +13566,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $643万
@@ -13566,7 +13574,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $992万
@@ -13574,7 +13582,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1019万
@@ -13582,7 +13590,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1019万
@@ -13590,7 +13598,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1042万
@@ -13598,8 +13606,8 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr"/>
-      <c r="J16" s="22" t="inlineStr"/>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -13607,7 +13615,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1436万
@@ -13615,7 +13623,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $936万
@@ -13623,7 +13631,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $633万
@@ -13631,7 +13639,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $982万
@@ -13639,7 +13647,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1001万
@@ -13647,7 +13655,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $1001万
@@ -13655,7 +13663,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $1022万
@@ -13663,8 +13671,8 @@
 (26年-09月-30日)</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr"/>
-      <c r="J17" s="22" t="inlineStr"/>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -13672,7 +13680,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1422万
@@ -13680,7 +13688,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $938万
@@ -13688,7 +13696,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $676万
@@ -13696,7 +13704,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $985万
@@ -13704,7 +13712,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $981万
@@ -13712,7 +13720,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $981万
@@ -13720,7 +13728,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $943万
@@ -13728,8 +13736,8 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr"/>
-      <c r="J18" s="22" t="inlineStr"/>
+      <c r="I18" s="21" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -13737,7 +13745,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 602呎 (3房)
 $1408万
@@ -13745,7 +13753,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 456呎 (2房)
 $936万
@@ -13753,7 +13761,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $674万
@@ -13761,7 +13769,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $1016万
@@ -13769,7 +13777,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 $1040万
@@ -13777,7 +13785,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>F | 433呎 (2房)
 $971万
@@ -13785,7 +13793,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 408呎 (2房)
 $934万
@@ -13793,8 +13801,8 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr"/>
-      <c r="J19" s="22" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -13802,7 +13810,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $962万
@@ -13810,7 +13818,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $903万
@@ -13818,7 +13826,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $658万
@@ -13826,7 +13834,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $945万
@@ -13834,7 +13842,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $662万
@@ -13842,7 +13850,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $662万
@@ -13850,7 +13858,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $709万
@@ -13858,7 +13866,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $675万
@@ -13866,7 +13874,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J20" s="21" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $744万
@@ -13881,7 +13889,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $956万
@@ -13889,7 +13897,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $898万
@@ -13897,7 +13905,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $621万
@@ -13905,7 +13913,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $940万
@@ -13913,7 +13921,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $665万
@@ -13921,7 +13929,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $657万
@@ -13929,7 +13937,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $667万
@@ -13937,7 +13945,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $719万
@@ -13945,7 +13953,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J21" s="21" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $749万
@@ -13960,7 +13968,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $951万
@@ -13968,7 +13976,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $912万
@@ -13976,7 +13984,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $619万
@@ -13984,7 +13992,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $939万
@@ -13992,7 +14000,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $660万
@@ -14000,7 +14008,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $660万
@@ -14008,7 +14016,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $663万
@@ -14016,7 +14024,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $676万
@@ -14024,7 +14032,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $745万
@@ -14039,7 +14047,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $930万
@@ -14047,7 +14055,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $892万
@@ -14055,7 +14063,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $617万
@@ -14063,7 +14071,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $982万
@@ -14071,7 +14079,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $692万
@@ -14079,7 +14087,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $655万
@@ -14087,7 +14095,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $659万
@@ -14095,7 +14103,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $672万
@@ -14103,7 +14111,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J23" s="21" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $782万
@@ -14118,7 +14126,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $920万
@@ -14126,7 +14134,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $881万
@@ -14134,7 +14142,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $651万
@@ -14142,7 +14150,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $923万
@@ -14150,7 +14158,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $650万
@@ -14158,7 +14166,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $641万
@@ -14166,7 +14174,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $692万
@@ -14174,7 +14182,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $668万
@@ -14182,7 +14190,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J24" s="21" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $778万
@@ -14197,7 +14205,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $967万
@@ -14205,7 +14213,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $876万
@@ -14213,7 +14221,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $614万
@@ -14221,7 +14229,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $970万
@@ -14229,7 +14237,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $681万
@@ -14237,7 +14245,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $644万
@@ -14245,7 +14253,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $651万
@@ -14253,7 +14261,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $664万
@@ -14261,7 +14269,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $773万
@@ -14276,7 +14284,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $961万
@@ -14284,7 +14292,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $926万
@@ -14292,7 +14300,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $610万
@@ -14300,7 +14308,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $962万
@@ -14308,7 +14316,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $676万
@@ -14316,7 +14324,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $676万
@@ -14324,7 +14332,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $682万
@@ -14332,7 +14340,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I26" s="21" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $696万
@@ -14340,7 +14348,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $767万
@@ -14355,7 +14363,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $960万
@@ -14363,7 +14371,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $882万
@@ -14371,7 +14379,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $606万
@@ -14379,7 +14387,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $907万
@@ -14387,7 +14395,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $670万
@@ -14395,7 +14403,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $670万
@@ -14403,7 +14411,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $641万
@@ -14411,7 +14419,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I27" s="21" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $653万
@@ -14419,7 +14427,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="J27" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $711万
@@ -14434,7 +14442,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $902万
@@ -14442,7 +14450,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $910万
@@ -14450,7 +14458,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $603万
@@ -14458,7 +14466,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $952万
@@ -14466,7 +14474,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $665万
@@ -14474,7 +14482,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $665万
@@ -14482,7 +14490,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H28" s="21" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $672万
@@ -14490,7 +14498,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I28" s="21" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $685万
@@ -14498,7 +14506,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $755万
@@ -14513,7 +14521,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $897万
@@ -14521,7 +14529,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $924万
@@ -14529,7 +14537,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $633万
@@ -14537,7 +14545,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $957万
@@ -14545,7 +14553,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $623万
@@ -14553,7 +14561,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $623万
@@ -14561,7 +14569,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $665万
@@ -14569,7 +14577,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $642万
@@ -14577,7 +14585,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J29" s="21" t="inlineStr">
+      <c r="J29" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $707万
@@ -14592,7 +14600,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $938万
@@ -14600,7 +14608,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $915万
@@ -14608,7 +14616,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 316呎 (1房)
 $596万
@@ -14616,7 +14624,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
 $897万
@@ -14624,7 +14632,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 304呎 (1房)
 $617万
@@ -14632,7 +14640,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $617万
@@ -14640,7 +14648,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $623万
@@ -14648,7 +14656,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $680万
@@ -14656,7 +14664,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J30" s="21" t="inlineStr">
+      <c r="J30" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $700万
@@ -14671,7 +14679,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 428呎 (2房)
 $901万
@@ -14679,7 +14687,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 453呎 (2房)
 $858万
@@ -14687,7 +14695,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 277呎 (1房)
 $831万
@@ -14695,7 +14703,7 @@
 (26年-09月-23日)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 413呎 (2房)
 $1239万
@@ -14703,7 +14711,7 @@
 (26年-10月-01日)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>E | 305呎 (1房)
 $607万
@@ -14711,7 +14719,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>F | 304呎 (1房)
 $605万
@@ -14719,7 +14727,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $611万
@@ -14727,7 +14735,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="I31" s="21" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>H | 304呎 (1房)
 $623万
@@ -14735,7 +14743,7 @@
 (26年-09月-26日)</t>
         </is>
       </c>
-      <c r="J31" s="21" t="inlineStr">
+      <c r="J31" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
 $686万

--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3292,14 +3292,14 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>11247000</v>
+        <v>11447000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>24938</v>
+        <v>25381</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>11247000</v>
+        <v>11447000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>24938</v>
+        <v>25381</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -8934,14 +8934,14 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
-        <v>7731000</v>
+        <v>7314000</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>25599</v>
+        <v>24219</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="K134" s="5" t="n">
-        <v>7731000</v>
+        <v>7314000</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>25599</v>
+        <v>24219</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -13209,7 +13209,7 @@
           <t>C | 799呎 (3房)
 $2557万
 $31,997/呎
-(26年-09月-19日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -13260,7 +13260,7 @@
           <t>C | 792呎 (3房)
 $2455万
 $31,000/呎
-(26年-09月-19日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -13327,7 +13327,7 @@
           <t>E | 433呎 (2房)
 $1121万
 $25,894/呎
-(26年-09月-26日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -13382,9 +13382,9 @@
       <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 451呎 (2房)
-$1125万
-$24,938/呎
-(26年-09月-30日)</t>
+$1145万
+$25,381/呎
+(26年-10月-10日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -13926,7 +13926,7 @@
           <t>E | 304呎 (1房)
 $665万
 $21,888/呎
-(26年-09月-26日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -13934,7 +13934,7 @@
           <t>F | 304呎 (1房)
 $657万
 $21,609/呎
-(26年-09月-26日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -14272,9 +14272,9 @@
       <c r="J25" s="22" t="inlineStr">
         <is>
           <t>J | 302呎 (1房)
-$773万
-$25,599/呎
-(26年-09月-30日)</t>
+$731万
+$24,219/呎
+(26年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -14353,7 +14353,7 @@
           <t>J | 302呎 (1房)
 $767万
 $25,391/呎
-(26年-09月-30日)</t>
+(26年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
           <t>C | 316呎 (1房)
 $596万
 $18,848/呎
-(26年-09月-26日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -14637,7 +14637,7 @@
           <t>E | 304呎 (1房)
 $617万
 $20,293/呎
-(26年-09月-26日)</t>
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">

--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13107,7 +13107,7 @@
           <t>C | 799呎 (3房)
 $3196万
 $40,000/呎
-(26年-09月-25日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -13123,7 +13123,7 @@
           <t>E | 432呎 (2房)
 $1301万
 $30,118/呎
-(26年-09月-30日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr"/>
@@ -13150,7 +13150,7 @@
           <t>B | 767呎 (3房)
 $2454万
 $32,000/呎
-(26年-09月-19日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -13158,7 +13158,7 @@
           <t>C | 799呎 (3房)
 $2716万
 $33,997/呎
-(26年-09月-23日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -13217,7 +13217,7 @@
           <t>D | 389呎 (2房)
 $1146万
 $29,455/呎
-(26年-09月-30日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -13295,7 +13295,7 @@
           <t>A | 602呎 (3房)
 $1647万
 $27,362/呎
-(26年-09月-30日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -13303,7 +13303,7 @@
           <t>B | 456呎 (2房)
 $951万
 $20,849/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -13465,7 +13465,7 @@
           <t>F | 433呎 (2房)
 $1122万
 $25,924/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -13530,7 +13530,7 @@
           <t>F | 433呎 (2房)
 $1095万
 $25,282/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -13563,7 +13563,7 @@
           <t>B | 456呎 (2房)
 $939万
 $20,596/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -13628,7 +13628,7 @@
           <t>B | 456呎 (2房)
 $936万
 $20,533/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -13652,7 +13652,7 @@
           <t>E | 433呎 (2房)
 $1001万
 $23,113/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -13815,7 +13815,7 @@
           <t>A | 428呎 (2房)
 $962万
 $22,470/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -13823,7 +13823,7 @@
           <t>B | 453呎 (2房)
 $903万
 $19,934/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -13839,7 +13839,7 @@
           <t>D | 451呎 (2房)
 $945万
 $20,962/呎
-(26年-09月-26日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -13847,7 +13847,7 @@
           <t>E | 304呎 (1房)
 $662万
 $21,783/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -13855,7 +13855,7 @@
           <t>F | 304呎 (1房)
 $662万
 $21,783/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -13863,7 +13863,7 @@
           <t>G | 301呎 (1房)
 $709万
 $23,551/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -13871,7 +13871,7 @@
           <t>H | 304呎 (1房)
 $675万
 $22,217/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -13894,7 +13894,7 @@
           <t>A | 428呎 (2房)
 $956万
 $22,332/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -13902,7 +13902,7 @@
           <t>B | 453呎 (2房)
 $898万
 $19,815/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -13910,7 +13910,7 @@
           <t>C | 316呎 (1房)
 $621万
 $19,652/呎
-(26年-09月-26日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -13918,7 +13918,7 @@
           <t>D | 451呎 (2房)
 $940万
 $20,836/呎
-(26年-09月-26日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -13942,7 +13942,7 @@
           <t>G | 301呎 (1房)
 $667万
 $22,146/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -13950,7 +13950,7 @@
           <t>H | 304呎 (1房)
 $719万
 $23,641/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -13973,7 +13973,7 @@
           <t>A | 428呎 (2房)
 $951万
 $22,217/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -13989,7 +13989,7 @@
           <t>C | 316呎 (1房)
 $619万
 $19,595/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -14021,7 +14021,7 @@
           <t>G | 301呎 (1房)
 $663万
 $22,017/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -14029,7 +14029,7 @@
           <t>H | 304呎 (1房)
 $676万
 $22,234/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -14139,7 +14139,7 @@
           <t>B | 453呎 (2房)
 $881万
 $19,455/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -14218,7 +14218,7 @@
           <t>B | 453呎 (2房)
 $876万
 $19,336/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -14408,7 +14408,7 @@
           <t>F | 304呎 (1房)
 $670万
 $22,056/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -14534,7 +14534,7 @@
           <t>B | 453呎 (2房)
 $924万
 $20,408/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -14542,7 +14542,7 @@
           <t>C | 316呎 (1房)
 $633万
 $20,041/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -14550,7 +14550,7 @@
           <t>D | 451呎 (2房)
 $957万
 $21,228/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -14566,7 +14566,7 @@
           <t>F | 304呎 (1房)
 $623万
 $20,497/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
@@ -14574,7 +14574,7 @@
           <t>G | 301呎 (1房)
 $665万
 $22,093/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -14582,7 +14582,7 @@
           <t>H | 304呎 (1房)
 $642万
 $21,112/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -14590,7 +14590,7 @@
           <t>J | 302呎 (1房)
 $707万
 $23,411/呎
-(26年-09月-30日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -14613,7 +14613,7 @@
           <t>B | 453呎 (2房)
 $915万
 $20,208/呎
-(26年-09月-26日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -14645,7 +14645,7 @@
           <t>F | 304呎 (1房)
 $617万
 $20,293/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
@@ -14653,7 +14653,7 @@
           <t>G | 301呎 (1房)
 $623万
 $20,698/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -14669,7 +14669,7 @@
           <t>J | 302呎 (1房)
 $700万
 $23,179/呎
-(26年-09月-30日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -14684,7 +14684,7 @@
           <t>A | 428呎 (2房)
 $901万
 $21,051/呎
-(26年-09月-26日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -14724,7 +14724,7 @@
           <t>F | 304呎 (1房)
 $605万
 $19,891/呎
-(26年-09月-26日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
@@ -14732,7 +14732,7 @@
           <t>G | 301呎 (1房)
 $611万
 $20,292/呎
-(26年-09月-26日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -14748,7 +14748,7 @@
           <t>J | 302呎 (1房)
 $686万
 $22,728/呎
-(26年-09月-30日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>

--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -1098,7 +1098,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12530,7 +12530,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -13072,7 +13072,7 @@
           <t>E | 432呎 (2房)
 $1334万
 $30,870/呎
-(26年-09月-30日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr"/>
@@ -13174,7 +13174,7 @@
           <t>E | 432呎 (2房)
 $1269万
 $29,382/呎
-(26年-09月-30日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr"/>
@@ -13311,7 +13311,7 @@
           <t>C | 316呎 (1房)
 $664万
 $21,006/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -13368,7 +13368,7 @@
           <t>B | 456呎 (2房)
 $948万
 $20,787/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -13376,7 +13376,7 @@
           <t>C | 316呎 (1房)
 $662万
 $20,943/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -13425,7 +13425,7 @@
           <t>A | 602呎 (3房)
 $1489万
 $24,731/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -13441,7 +13441,7 @@
           <t>C | 316呎 (1房)
 $660万
 $20,880/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -13457,7 +13457,7 @@
           <t>E | 433呎 (2房)
 $1122万
 $25,924/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -13490,7 +13490,7 @@
           <t>A | 602呎 (3房)
 $1466万
 $24,346/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -13514,7 +13514,7 @@
           <t>D | 451呎 (2房)
 $995万
 $22,055/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -13522,7 +13522,7 @@
           <t>E | 433呎 (2房)
 $1035万
 $23,894/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -13879,7 +13879,7 @@
           <t>J | 302呎 (1房)
 $744万
 $24,639/呎
-(26年-09月-30日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -13997,7 +13997,7 @@
           <t>D | 451呎 (2房)
 $939万
 $20,818/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -14005,7 +14005,7 @@
           <t>E | 304呎 (1房)
 $660万
 $21,711/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -14013,7 +14013,7 @@
           <t>F | 304呎 (1房)
 $660万
 $21,711/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -14052,7 +14052,7 @@
           <t>A | 428呎 (2房)
 $930万
 $21,734/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -14076,7 +14076,7 @@
           <t>D | 451呎 (2房)
 $982万
 $21,778/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -14084,7 +14084,7 @@
           <t>E | 304呎 (1房)
 $692万
 $22,770/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -14100,7 +14100,7 @@
           <t>G | 301呎 (1房)
 $659万
 $21,884/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -14108,7 +14108,7 @@
           <t>H | 304呎 (1房)
 $672万
 $22,105/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -14147,7 +14147,7 @@
           <t>C | 316呎 (1房)
 $651万
 $20,592/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -14155,7 +14155,7 @@
           <t>D | 451呎 (2房)
 $923万
 $20,457/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -14171,7 +14171,7 @@
           <t>F | 304呎 (1房)
 $641万
 $21,095/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -14242,7 +14242,7 @@
           <t>E | 304呎 (1房)
 $681万
 $22,408/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -14297,7 +14297,7 @@
           <t>B | 453呎 (2房)
 $926万
 $20,446/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -14376,7 +14376,7 @@
           <t>B | 453呎 (2房)
 $882万
 $19,459/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -14384,7 +14384,7 @@
           <t>C | 316呎 (1房)
 $606万
 $19,190/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -14463,7 +14463,7 @@
           <t>C | 316呎 (1房)
 $603万
 $19,076/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -14661,7 +14661,7 @@
           <t>H | 304呎 (1房)
 $680万
 $22,362/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -14700,7 +14700,7 @@
           <t>C | 277呎 (1房)
 $831万
 $30,000/呎
-(26年-09月-23日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -14716,7 +14716,7 @@
           <t>E | 305呎 (1房)
 $607万
 $19,895/呎
-(26年-09月-26日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">

--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -974,7 +974,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -13010,7 +13010,7 @@
           <t>A | 1465呎 (2房)
 $5860万
 $40,000/呎
-(26年-09月-19日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -13018,7 +13018,7 @@
           <t>B | 1393呎 (2房)
 $5851万
 $42,000/呎
-(26年-09月-19日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -13064,7 +13064,7 @@
           <t>D | 389呎 (2房)
 $1306万
 $33,578/呎
-(26年-09月-30日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -13115,7 +13115,7 @@
           <t>D | 389呎 (2房)
 $1269万
 $32,620/呎
-(26年-09月-30日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -13166,7 +13166,7 @@
           <t>D | 389呎 (2房)
 $1238万
 $31,812/呎
-(26年-09月-30日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -13225,7 +13225,7 @@
           <t>E | 432呎 (2房)
 $1234万
 $28,572/呎
-(26年-09月-30日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr"/>
@@ -13244,7 +13244,7 @@
           <t>A | 610呎 (3房)
 $1830万
 $30,000/呎
-(26年-09月-19日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -13268,7 +13268,7 @@
           <t>D | 389呎 (2房)
 $1197万
 $30,771/呎
-(26年-09月-30日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -13276,7 +13276,7 @@
           <t>E | 432呎 (2房)
 $1204万
 $27,863/呎
-(26年-09月-30日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr"/>
@@ -13319,7 +13319,7 @@
           <t>D | 450呎 (2房)
 $1229万
 $27,320/呎
-(26年-09月-30日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -13335,7 +13335,7 @@
           <t>F | 433呎 (2房)
 $1186万
 $27,388/呎
-(26年-09月-26日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -13343,7 +13343,7 @@
           <t>G | 408呎 (2房)
 $1125万
 $27,574/呎
-(26年-09月-30日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr"/>
@@ -13360,7 +13360,7 @@
           <t>A | 602呎 (3房)
 $1511万
 $25,101/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -13384,7 +13384,7 @@
           <t>D | 451呎 (2房)
 $1145万
 $25,381/呎
-(26年-10月-10日)</t>
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -13392,7 +13392,7 @@
           <t>E | 433呎 (2房)
 $1158万
 $26,741/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -13400,7 +13400,7 @@
           <t>F | 433呎 (2房)
 $1108万
 $25,587/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -13408,7 +13408,7 @@
           <t>G | 408呎 (2房)
 $1161万
 $28,449/呎
-(26年-09月-30日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr"/>
@@ -13433,7 +13433,7 @@
           <t>B | 456呎 (2房)
 $950万
 $20,833/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -13449,7 +13449,7 @@
           <t>D | 451呎 (2房)
 $1169万
 $25,918/呎
-(26年-09月-30日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -13473,7 +13473,7 @@
           <t>G | 408呎 (2房)
 $1132万
 $27,740/呎
-(26年-09月-30日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr"/>
@@ -13498,7 +13498,7 @@
           <t>B | 456呎 (2房)
 $1002万
 $21,971/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -13506,7 +13506,7 @@
           <t>C | 316呎 (1房)
 $645万
 $20,408/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -13538,7 +13538,7 @@
           <t>G | 408呎 (2房)
 $1048万
 $25,691/呎
-(26年-09月-30日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
           <t>A | 602呎 (3房)
 $1451万
 $24,101/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -13571,7 +13571,7 @@
           <t>C | 316呎 (1房)
 $643万
 $20,348/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -13579,7 +13579,7 @@
           <t>D | 451呎 (2房)
 $992万
 $21,993/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -13587,7 +13587,7 @@
           <t>E | 433呎 (2房)
 $1019万
 $23,531/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -13595,7 +13595,7 @@
           <t>F | 433呎 (2房)
 $1019万
 $23,531/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -13603,7 +13603,7 @@
           <t>G | 408呎 (2房)
 $1042万
 $25,549/呎
-(26年-09月-30日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr"/>
@@ -13620,7 +13620,7 @@
           <t>A | 602呎 (3房)
 $1436万
 $23,859/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -13636,7 +13636,7 @@
           <t>C | 316呎 (1房)
 $633万
 $20,032/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -13644,7 +13644,7 @@
           <t>D | 451呎 (2房)
 $982万
 $21,774/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -13660,7 +13660,7 @@
           <t>F | 433呎 (2房)
 $1001万
 $23,113/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -13668,7 +13668,7 @@
           <t>G | 408呎 (2房)
 $1022万
 $25,049/呎
-(26年-09月-30日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr"/>
@@ -13685,7 +13685,7 @@
           <t>A | 602呎 (3房)
 $1422万
 $23,620/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -13693,7 +13693,7 @@
           <t>B | 456呎 (2房)
 $938万
 $20,581/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -13701,7 +13701,7 @@
           <t>C | 316呎 (1房)
 $676万
 $21,383/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -13709,7 +13709,7 @@
           <t>D | 451呎 (2房)
 $985万
 $21,836/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -13717,7 +13717,7 @@
           <t>E | 433呎 (2房)
 $981万
 $22,658/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -13725,7 +13725,7 @@
           <t>F | 433呎 (2房)
 $981万
 $22,658/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -13733,7 +13733,7 @@
           <t>G | 408呎 (2房)
 $943万
 $23,113/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr"/>
@@ -13750,7 +13750,7 @@
           <t>A | 602呎 (3房)
 $1408万
 $23,384/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -13758,7 +13758,7 @@
           <t>B | 456呎 (2房)
 $936万
 $20,518/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -13766,7 +13766,7 @@
           <t>C | 316呎 (1房)
 $674万
 $21,316/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -13774,7 +13774,7 @@
           <t>D | 451呎 (2房)
 $1016万
 $22,521/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -13782,7 +13782,7 @@
           <t>E | 433呎 (2房)
 $1040万
 $24,016/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -13790,7 +13790,7 @@
           <t>F | 433呎 (2房)
 $971万
 $22,434/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -13798,7 +13798,7 @@
           <t>G | 408呎 (2房)
 $934万
 $22,882/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr"/>
@@ -13831,7 +13831,7 @@
           <t>C | 316呎 (1房)
 $658万
 $20,839/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -13958,7 +13958,7 @@
           <t>J | 302呎 (1房)
 $749万
 $24,805/呎
-(26年-09月-30日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -13981,7 +13981,7 @@
           <t>B | 453呎 (2房)
 $912万
 $20,135/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -14037,7 +14037,7 @@
           <t>J | 302呎 (1房)
 $745万
 $24,659/呎
-(26年-09月-30日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -14060,7 +14060,7 @@
           <t>B | 453呎 (2房)
 $892万
 $19,682/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -14068,7 +14068,7 @@
           <t>C | 316呎 (1房)
 $617万
 $19,538/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -14092,7 +14092,7 @@
           <t>F | 304呎 (1房)
 $655万
 $21,543/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -14116,7 +14116,7 @@
           <t>J | 302呎 (1房)
 $782万
 $25,904/呎
-(26年-09月-30日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
           <t>A | 428呎 (2房)
 $920万
 $21,486/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -14163,7 +14163,7 @@
           <t>E | 304呎 (1房)
 $650万
 $21,368/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -14179,7 +14179,7 @@
           <t>G | 301呎 (1房)
 $692万
 $22,993/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -14187,7 +14187,7 @@
           <t>H | 304呎 (1房)
 $668万
 $21,970/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -14195,7 +14195,7 @@
           <t>J | 302呎 (1房)
 $778万
 $25,752/呎
-(26年-09月-30日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
           <t>A | 428呎 (2房)
 $967万
 $22,598/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -14226,7 +14226,7 @@
           <t>C | 316呎 (1房)
 $614万
 $19,418/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -14234,7 +14234,7 @@
           <t>D | 451呎 (2房)
 $970万
 $21,514/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -14250,7 +14250,7 @@
           <t>F | 304呎 (1房)
 $644万
 $21,201/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -14258,7 +14258,7 @@
           <t>G | 301呎 (1房)
 $651万
 $21,625/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -14266,7 +14266,7 @@
           <t>H | 304呎 (1房)
 $664万
 $21,842/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -14289,7 +14289,7 @@
           <t>A | 428呎 (2房)
 $961万
 $22,458/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -14305,7 +14305,7 @@
           <t>C | 316呎 (1房)
 $610万
 $19,304/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -14313,7 +14313,7 @@
           <t>D | 451呎 (2房)
 $962万
 $21,339/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -14321,7 +14321,7 @@
           <t>E | 304呎 (1房)
 $676万
 $22,230/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -14329,7 +14329,7 @@
           <t>F | 304呎 (1房)
 $676万
 $22,230/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -14337,7 +14337,7 @@
           <t>G | 301呎 (1房)
 $682万
 $22,674/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -14345,7 +14345,7 @@
           <t>H | 304呎 (1房)
 $696万
 $22,901/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -14368,7 +14368,7 @@
           <t>A | 428呎 (2房)
 $960万
 $22,442/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -14392,7 +14392,7 @@
           <t>D | 451呎 (2房)
 $907万
 $20,113/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -14400,7 +14400,7 @@
           <t>E | 304呎 (1房)
 $670万
 $22,056/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -14416,7 +14416,7 @@
           <t>G | 301呎 (1房)
 $641万
 $21,282/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -14424,7 +14424,7 @@
           <t>H | 304呎 (1房)
 $653万
 $21,493/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -14432,7 +14432,7 @@
           <t>J | 302呎 (1房)
 $711万
 $23,536/呎
-(26年-09月-30日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -14447,7 +14447,7 @@
           <t>A | 428呎 (2房)
 $902万
 $21,084/呎
-(26年-09月-26日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -14471,7 +14471,7 @@
           <t>D | 451呎 (2房)
 $952万
 $21,106/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -14479,7 +14479,7 @@
           <t>E | 304呎 (1房)
 $665万
 $21,875/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -14487,7 +14487,7 @@
           <t>F | 304呎 (1房)
 $665万
 $21,875/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -14511,7 +14511,7 @@
           <t>J | 302呎 (1房)
 $755万
 $24,993/呎
-(26年-09月-30日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -14526,7 +14526,7 @@
           <t>A | 428呎 (2房)
 $897万
 $20,956/呎
-(26年-09月-26日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -14558,7 +14558,7 @@
           <t>E | 304呎 (1房)
 $623万
 $20,497/呎
-(26年-09月-26日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -14629,7 +14629,7 @@
           <t>D | 451呎 (2房)
 $897万
 $19,885/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -14740,7 +14740,7 @@
           <t>H | 304呎 (1房)
 $623万
 $20,497/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">

--- a/港岛-北角-皇璇/皇璇_销控明细表.xlsx
+++ b/港岛-北角-皇璇/皇璇_销控明细表.xlsx
@@ -12592,7 +12592,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -14708,7 +14708,7 @@
           <t>D | 413呎 (2房)
 $1239万
 $30,000/呎
-(26年-10月-01日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
